--- a/stowe.xlsx
+++ b/stowe.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B38B0528-D7AD-47A6-9D70-2C6410247377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{95C94501-5EB8-428A-81C9-65E6C5121629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3004" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3387" uniqueCount="486">
   <si>
     <t>Scheme Listing by CRID for ZIP Code 05672</t>
   </si>
@@ -1004,7 +1004,7 @@
     <t>PINNACLE</t>
   </si>
   <si>
-    <t>POINTS</t>
+    <t>POINTS NORTH</t>
   </si>
   <si>
     <t>POND</t>
@@ -1466,20 +1466,20 @@
     <t>YORIERRY</t>
   </si>
   <si>
-    <t>Total Line items: 374</t>
+    <t>Total Line items: 375</t>
   </si>
   <si>
     <t>zip code</t>
+  </si>
+  <si>
+    <t>05672</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="00000"/>
-  </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1491,6 +1491,13 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1531,10 +1538,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1874,7 +1881,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I377"/>
+  <dimension ref="A1:I378"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="8" customWidth="1"/>
@@ -1940,8 +1947,8 @@
       <c r="G3" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="8">
-        <v>5672</v>
+      <c r="H3" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>11</v>
@@ -1969,8 +1976,8 @@
       <c r="G4" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="8">
-        <v>5672</v>
+      <c r="H4" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>15</v>
@@ -1998,8 +2005,8 @@
       <c r="G5" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="8">
-        <v>5672</v>
+      <c r="H5" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>18</v>
@@ -2027,8 +2034,8 @@
       <c r="G6" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="8">
-        <v>5672</v>
+      <c r="H6" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>22</v>
@@ -2056,8 +2063,8 @@
       <c r="G7" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="8">
-        <v>5672</v>
+      <c r="H7" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>18</v>
@@ -2085,8 +2092,8 @@
       <c r="G8" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="8">
-        <v>5672</v>
+      <c r="H8" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>18</v>
@@ -2114,8 +2121,8 @@
       <c r="G9" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="8">
-        <v>5672</v>
+      <c r="H9" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>22</v>
@@ -2143,8 +2150,8 @@
       <c r="G10" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="8">
-        <v>5672</v>
+      <c r="H10" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>18</v>
@@ -2172,8 +2179,8 @@
       <c r="G11" t="s">
         <v>8</v>
       </c>
-      <c r="H11" s="8">
-        <v>5672</v>
+      <c r="H11" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>18</v>
@@ -2201,8 +2208,8 @@
       <c r="G12" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="8">
-        <v>5672</v>
+      <c r="H12" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>15</v>
@@ -2230,8 +2237,8 @@
       <c r="G13" t="s">
         <v>8</v>
       </c>
-      <c r="H13" s="8">
-        <v>5672</v>
+      <c r="H13" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>18</v>
@@ -2259,8 +2266,8 @@
       <c r="G14" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="8">
-        <v>5672</v>
+      <c r="H14" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>18</v>
@@ -2288,8 +2295,8 @@
       <c r="G15" t="s">
         <v>8</v>
       </c>
-      <c r="H15" s="8">
-        <v>5672</v>
+      <c r="H15" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>15</v>
@@ -2317,8 +2324,8 @@
       <c r="G16" t="s">
         <v>8</v>
       </c>
-      <c r="H16" s="8">
-        <v>5672</v>
+      <c r="H16" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>15</v>
@@ -2346,8 +2353,8 @@
       <c r="G17" t="s">
         <v>8</v>
       </c>
-      <c r="H17" s="8">
-        <v>5672</v>
+      <c r="H17" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>22</v>
@@ -2375,8 +2382,8 @@
       <c r="G18" t="s">
         <v>8</v>
       </c>
-      <c r="H18" s="8">
-        <v>5672</v>
+      <c r="H18" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>22</v>
@@ -2404,8 +2411,8 @@
       <c r="G19" t="s">
         <v>8</v>
       </c>
-      <c r="H19" s="8">
-        <v>5672</v>
+      <c r="H19" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>11</v>
@@ -2433,8 +2440,8 @@
       <c r="G20" t="s">
         <v>8</v>
       </c>
-      <c r="H20" s="8">
-        <v>5672</v>
+      <c r="H20" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>15</v>
@@ -2462,8 +2469,8 @@
       <c r="G21" t="s">
         <v>8</v>
       </c>
-      <c r="H21" s="8">
-        <v>5672</v>
+      <c r="H21" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>15</v>
@@ -2491,8 +2498,8 @@
       <c r="G22" t="s">
         <v>8</v>
       </c>
-      <c r="H22" s="8">
-        <v>5672</v>
+      <c r="H22" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>18</v>
@@ -2520,8 +2527,8 @@
       <c r="G23" t="s">
         <v>8</v>
       </c>
-      <c r="H23" s="8">
-        <v>5672</v>
+      <c r="H23" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>60</v>
@@ -2549,8 +2556,8 @@
       <c r="G24" t="s">
         <v>8</v>
       </c>
-      <c r="H24" s="8">
-        <v>5672</v>
+      <c r="H24" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>22</v>
@@ -2578,8 +2585,8 @@
       <c r="G25" t="s">
         <v>8</v>
       </c>
-      <c r="H25" s="8">
-        <v>5672</v>
+      <c r="H25" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>18</v>
@@ -2607,8 +2614,8 @@
       <c r="G26" t="s">
         <v>8</v>
       </c>
-      <c r="H26" s="8">
-        <v>5672</v>
+      <c r="H26" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>11</v>
@@ -2636,8 +2643,8 @@
       <c r="G27" t="s">
         <v>8</v>
       </c>
-      <c r="H27" s="8">
-        <v>5672</v>
+      <c r="H27" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>11</v>
@@ -2665,8 +2672,8 @@
       <c r="G28" t="s">
         <v>8</v>
       </c>
-      <c r="H28" s="8">
-        <v>5672</v>
+      <c r="H28" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>15</v>
@@ -2694,8 +2701,8 @@
       <c r="G29" t="s">
         <v>8</v>
       </c>
-      <c r="H29" s="8">
-        <v>5672</v>
+      <c r="H29" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>22</v>
@@ -2723,8 +2730,8 @@
       <c r="G30" t="s">
         <v>8</v>
       </c>
-      <c r="H30" s="8">
-        <v>5672</v>
+      <c r="H30" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>15</v>
@@ -2752,8 +2759,8 @@
       <c r="G31" t="s">
         <v>8</v>
       </c>
-      <c r="H31" s="8">
-        <v>5672</v>
+      <c r="H31" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>22</v>
@@ -2781,8 +2788,8 @@
       <c r="G32" t="s">
         <v>8</v>
       </c>
-      <c r="H32" s="8">
-        <v>5672</v>
+      <c r="H32" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>11</v>
@@ -2810,8 +2817,8 @@
       <c r="G33" t="s">
         <v>8</v>
       </c>
-      <c r="H33" s="8">
-        <v>5672</v>
+      <c r="H33" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>11</v>
@@ -2839,8 +2846,8 @@
       <c r="G34" t="s">
         <v>8</v>
       </c>
-      <c r="H34" s="8">
-        <v>5672</v>
+      <c r="H34" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>60</v>
@@ -2868,8 +2875,8 @@
       <c r="G35" t="s">
         <v>8</v>
       </c>
-      <c r="H35" s="8">
-        <v>5672</v>
+      <c r="H35" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>11</v>
@@ -2897,8 +2904,8 @@
       <c r="G36" t="s">
         <v>8</v>
       </c>
-      <c r="H36" s="8">
-        <v>5672</v>
+      <c r="H36" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>60</v>
@@ -2926,8 +2933,8 @@
       <c r="G37" t="s">
         <v>8</v>
       </c>
-      <c r="H37" s="8">
-        <v>5672</v>
+      <c r="H37" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>22</v>
@@ -2955,8 +2962,8 @@
       <c r="G38" t="s">
         <v>8</v>
       </c>
-      <c r="H38" s="8">
-        <v>5672</v>
+      <c r="H38" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>60</v>
@@ -2984,8 +2991,8 @@
       <c r="G39" t="s">
         <v>8</v>
       </c>
-      <c r="H39" s="8">
-        <v>5672</v>
+      <c r="H39" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>22</v>
@@ -3013,8 +3020,8 @@
       <c r="G40" t="s">
         <v>8</v>
       </c>
-      <c r="H40" s="8">
-        <v>5672</v>
+      <c r="H40" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>15</v>
@@ -3042,8 +3049,8 @@
       <c r="G41" t="s">
         <v>8</v>
       </c>
-      <c r="H41" s="8">
-        <v>5672</v>
+      <c r="H41" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>18</v>
@@ -3071,8 +3078,8 @@
       <c r="G42" t="s">
         <v>8</v>
       </c>
-      <c r="H42" s="8">
-        <v>5672</v>
+      <c r="H42" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>22</v>
@@ -3100,8 +3107,8 @@
       <c r="G43" t="s">
         <v>8</v>
       </c>
-      <c r="H43" s="8">
-        <v>5672</v>
+      <c r="H43" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>11</v>
@@ -3129,8 +3136,8 @@
       <c r="G44" t="s">
         <v>8</v>
       </c>
-      <c r="H44" s="8">
-        <v>5672</v>
+      <c r="H44" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>22</v>
@@ -3158,8 +3165,8 @@
       <c r="G45" t="s">
         <v>8</v>
       </c>
-      <c r="H45" s="8">
-        <v>5672</v>
+      <c r="H45" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>18</v>
@@ -3187,8 +3194,8 @@
       <c r="G46" t="s">
         <v>8</v>
       </c>
-      <c r="H46" s="8">
-        <v>5672</v>
+      <c r="H46" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>18</v>
@@ -3216,8 +3223,8 @@
       <c r="G47" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="8">
-        <v>5672</v>
+      <c r="H47" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>18</v>
@@ -3245,8 +3252,8 @@
       <c r="G48" t="s">
         <v>8</v>
       </c>
-      <c r="H48" s="8">
-        <v>5672</v>
+      <c r="H48" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>60</v>
@@ -3274,8 +3281,8 @@
       <c r="G49" t="s">
         <v>8</v>
       </c>
-      <c r="H49" s="8">
-        <v>5672</v>
+      <c r="H49" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>15</v>
@@ -3303,8 +3310,8 @@
       <c r="G50" t="s">
         <v>8</v>
       </c>
-      <c r="H50" s="8">
-        <v>5672</v>
+      <c r="H50" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>18</v>
@@ -3332,8 +3339,8 @@
       <c r="G51" t="s">
         <v>8</v>
       </c>
-      <c r="H51" s="8">
-        <v>5672</v>
+      <c r="H51" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>15</v>
@@ -3361,8 +3368,8 @@
       <c r="G52" t="s">
         <v>8</v>
       </c>
-      <c r="H52" s="8">
-        <v>5672</v>
+      <c r="H52" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>60</v>
@@ -3390,8 +3397,8 @@
       <c r="G53" t="s">
         <v>8</v>
       </c>
-      <c r="H53" s="8">
-        <v>5672</v>
+      <c r="H53" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>22</v>
@@ -3419,8 +3426,8 @@
       <c r="G54" t="s">
         <v>8</v>
       </c>
-      <c r="H54" s="8">
-        <v>5672</v>
+      <c r="H54" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>18</v>
@@ -3448,8 +3455,8 @@
       <c r="G55" t="s">
         <v>8</v>
       </c>
-      <c r="H55" s="8">
-        <v>5672</v>
+      <c r="H55" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>15</v>
@@ -3477,8 +3484,8 @@
       <c r="G56" t="s">
         <v>8</v>
       </c>
-      <c r="H56" s="8">
-        <v>5672</v>
+      <c r="H56" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>22</v>
@@ -3506,8 +3513,8 @@
       <c r="G57" t="s">
         <v>8</v>
       </c>
-      <c r="H57" s="8">
-        <v>5672</v>
+      <c r="H57" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>22</v>
@@ -3535,8 +3542,8 @@
       <c r="G58" t="s">
         <v>8</v>
       </c>
-      <c r="H58" s="8">
-        <v>5672</v>
+      <c r="H58" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>11</v>
@@ -3564,8 +3571,8 @@
       <c r="G59" t="s">
         <v>8</v>
       </c>
-      <c r="H59" s="8">
-        <v>5672</v>
+      <c r="H59" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>60</v>
@@ -3593,8 +3600,8 @@
       <c r="G60" t="s">
         <v>8</v>
       </c>
-      <c r="H60" s="8">
-        <v>5672</v>
+      <c r="H60" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>113</v>
@@ -3622,8 +3629,8 @@
       <c r="G61" t="s">
         <v>8</v>
       </c>
-      <c r="H61" s="8">
-        <v>5672</v>
+      <c r="H61" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>114</v>
@@ -3651,8 +3658,8 @@
       <c r="G62" t="s">
         <v>8</v>
       </c>
-      <c r="H62" s="8">
-        <v>5672</v>
+      <c r="H62" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>22</v>
@@ -3680,8 +3687,8 @@
       <c r="G63" t="s">
         <v>8</v>
       </c>
-      <c r="H63" s="8">
-        <v>5672</v>
+      <c r="H63" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>60</v>
@@ -3709,8 +3716,8 @@
       <c r="G64" t="s">
         <v>8</v>
       </c>
-      <c r="H64" s="8">
-        <v>5672</v>
+      <c r="H64" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>15</v>
@@ -3738,8 +3745,8 @@
       <c r="G65" t="s">
         <v>8</v>
       </c>
-      <c r="H65" s="8">
-        <v>5672</v>
+      <c r="H65" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>15</v>
@@ -3767,8 +3774,8 @@
       <c r="G66" t="s">
         <v>8</v>
       </c>
-      <c r="H66" s="8">
-        <v>5672</v>
+      <c r="H66" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>18</v>
@@ -3796,8 +3803,8 @@
       <c r="G67" t="s">
         <v>8</v>
       </c>
-      <c r="H67" s="8">
-        <v>5672</v>
+      <c r="H67" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>60</v>
@@ -3825,8 +3832,8 @@
       <c r="G68" t="s">
         <v>8</v>
       </c>
-      <c r="H68" s="8">
-        <v>5672</v>
+      <c r="H68" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>22</v>
@@ -3854,8 +3861,8 @@
       <c r="G69" t="s">
         <v>8</v>
       </c>
-      <c r="H69" s="8">
-        <v>5672</v>
+      <c r="H69" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>15</v>
@@ -3883,8 +3890,8 @@
       <c r="G70" t="s">
         <v>8</v>
       </c>
-      <c r="H70" s="8">
-        <v>5672</v>
+      <c r="H70" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>15</v>
@@ -3912,8 +3919,8 @@
       <c r="G71" t="s">
         <v>8</v>
       </c>
-      <c r="H71" s="8">
-        <v>5672</v>
+      <c r="H71" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>128</v>
@@ -3941,8 +3948,8 @@
       <c r="G72" t="s">
         <v>8</v>
       </c>
-      <c r="H72" s="8">
-        <v>5672</v>
+      <c r="H72" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>18</v>
@@ -3970,8 +3977,8 @@
       <c r="G73" t="s">
         <v>8</v>
       </c>
-      <c r="H73" s="8">
-        <v>5672</v>
+      <c r="H73" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>18</v>
@@ -3999,8 +4006,8 @@
       <c r="G74" t="s">
         <v>8</v>
       </c>
-      <c r="H74" s="8">
-        <v>5672</v>
+      <c r="H74" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>18</v>
@@ -4028,8 +4035,8 @@
       <c r="G75" t="s">
         <v>8</v>
       </c>
-      <c r="H75" s="8">
-        <v>5672</v>
+      <c r="H75" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>18</v>
@@ -4057,8 +4064,8 @@
       <c r="G76" t="s">
         <v>8</v>
       </c>
-      <c r="H76" s="8">
-        <v>5672</v>
+      <c r="H76" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>60</v>
@@ -4086,8 +4093,8 @@
       <c r="G77" t="s">
         <v>8</v>
       </c>
-      <c r="H77" s="8">
-        <v>5672</v>
+      <c r="H77" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>60</v>
@@ -4115,8 +4122,8 @@
       <c r="G78" t="s">
         <v>8</v>
       </c>
-      <c r="H78" s="8">
-        <v>5672</v>
+      <c r="H78" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>22</v>
@@ -4144,8 +4151,8 @@
       <c r="G79" t="s">
         <v>8</v>
       </c>
-      <c r="H79" s="8">
-        <v>5672</v>
+      <c r="H79" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>18</v>
@@ -4173,8 +4180,8 @@
       <c r="G80" t="s">
         <v>8</v>
       </c>
-      <c r="H80" s="8">
-        <v>5672</v>
+      <c r="H80" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>15</v>
@@ -4202,8 +4209,8 @@
       <c r="G81" t="s">
         <v>8</v>
       </c>
-      <c r="H81" s="8">
-        <v>5672</v>
+      <c r="H81" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>60</v>
@@ -4231,8 +4238,8 @@
       <c r="G82" t="s">
         <v>8</v>
       </c>
-      <c r="H82" s="8">
-        <v>5672</v>
+      <c r="H82" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>15</v>
@@ -4260,8 +4267,8 @@
       <c r="G83" t="s">
         <v>8</v>
       </c>
-      <c r="H83" s="8">
-        <v>5672</v>
+      <c r="H83" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>128</v>
@@ -4289,8 +4296,8 @@
       <c r="G84" t="s">
         <v>8</v>
       </c>
-      <c r="H84" s="8">
-        <v>5672</v>
+      <c r="H84" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>22</v>
@@ -4318,8 +4325,8 @@
       <c r="G85" t="s">
         <v>8</v>
       </c>
-      <c r="H85" s="8">
-        <v>5672</v>
+      <c r="H85" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>15</v>
@@ -4347,8 +4354,8 @@
       <c r="G86" t="s">
         <v>8</v>
       </c>
-      <c r="H86" s="8">
-        <v>5672</v>
+      <c r="H86" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>60</v>
@@ -4376,8 +4383,8 @@
       <c r="G87" t="s">
         <v>8</v>
       </c>
-      <c r="H87" s="8">
-        <v>5672</v>
+      <c r="H87" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>15</v>
@@ -4405,8 +4412,8 @@
       <c r="G88" t="s">
         <v>8</v>
       </c>
-      <c r="H88" s="8">
-        <v>5672</v>
+      <c r="H88" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>11</v>
@@ -4434,8 +4441,8 @@
       <c r="G89" t="s">
         <v>8</v>
       </c>
-      <c r="H89" s="8">
-        <v>5672</v>
+      <c r="H89" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>22</v>
@@ -4463,8 +4470,8 @@
       <c r="G90" t="s">
         <v>8</v>
       </c>
-      <c r="H90" s="8">
-        <v>5672</v>
+      <c r="H90" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>22</v>
@@ -4492,8 +4499,8 @@
       <c r="G91" t="s">
         <v>8</v>
       </c>
-      <c r="H91" s="8">
-        <v>5672</v>
+      <c r="H91" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>60</v>
@@ -4521,8 +4528,8 @@
       <c r="G92" t="s">
         <v>8</v>
       </c>
-      <c r="H92" s="8">
-        <v>5672</v>
+      <c r="H92" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>18</v>
@@ -4550,8 +4557,8 @@
       <c r="G93" t="s">
         <v>8</v>
       </c>
-      <c r="H93" s="8">
-        <v>5672</v>
+      <c r="H93" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>22</v>
@@ -4579,8 +4586,8 @@
       <c r="G94" t="s">
         <v>8</v>
       </c>
-      <c r="H94" s="8">
-        <v>5672</v>
+      <c r="H94" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>22</v>
@@ -4608,8 +4615,8 @@
       <c r="G95" t="s">
         <v>8</v>
       </c>
-      <c r="H95" s="8">
-        <v>5672</v>
+      <c r="H95" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>15</v>
@@ -4637,8 +4644,8 @@
       <c r="G96" t="s">
         <v>8</v>
       </c>
-      <c r="H96" s="8">
-        <v>5672</v>
+      <c r="H96" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>60</v>
@@ -4666,8 +4673,8 @@
       <c r="G97" t="s">
         <v>8</v>
       </c>
-      <c r="H97" s="8">
-        <v>5672</v>
+      <c r="H97" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>15</v>
@@ -4695,8 +4702,8 @@
       <c r="G98" t="s">
         <v>8</v>
       </c>
-      <c r="H98" s="8">
-        <v>5672</v>
+      <c r="H98" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>15</v>
@@ -4724,8 +4731,8 @@
       <c r="G99" t="s">
         <v>8</v>
       </c>
-      <c r="H99" s="8">
-        <v>5672</v>
+      <c r="H99" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>22</v>
@@ -4753,8 +4760,8 @@
       <c r="G100" t="s">
         <v>8</v>
       </c>
-      <c r="H100" s="8">
-        <v>5672</v>
+      <c r="H100" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>60</v>
@@ -4782,8 +4789,8 @@
       <c r="G101" t="s">
         <v>8</v>
       </c>
-      <c r="H101" s="8">
-        <v>5672</v>
+      <c r="H101" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>11</v>
@@ -4811,8 +4818,8 @@
       <c r="G102" t="s">
         <v>8</v>
       </c>
-      <c r="H102" s="8">
-        <v>5672</v>
+      <c r="H102" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>22</v>
@@ -4840,8 +4847,8 @@
       <c r="G103" t="s">
         <v>8</v>
       </c>
-      <c r="H103" s="8">
-        <v>5672</v>
+      <c r="H103" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>22</v>
@@ -4869,8 +4876,8 @@
       <c r="G104" t="s">
         <v>8</v>
       </c>
-      <c r="H104" s="8">
-        <v>5672</v>
+      <c r="H104" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>11</v>
@@ -4898,8 +4905,8 @@
       <c r="G105" t="s">
         <v>8</v>
       </c>
-      <c r="H105" s="8">
-        <v>5672</v>
+      <c r="H105" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>22</v>
@@ -4927,8 +4934,8 @@
       <c r="G106" t="s">
         <v>8</v>
       </c>
-      <c r="H106" s="8">
-        <v>5672</v>
+      <c r="H106" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>15</v>
@@ -4956,8 +4963,8 @@
       <c r="G107" t="s">
         <v>8</v>
       </c>
-      <c r="H107" s="8">
-        <v>5672</v>
+      <c r="H107" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>15</v>
@@ -4985,8 +4992,8 @@
       <c r="G108" t="s">
         <v>8</v>
       </c>
-      <c r="H108" s="8">
-        <v>5672</v>
+      <c r="H108" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>60</v>
@@ -5014,8 +5021,8 @@
       <c r="G109" t="s">
         <v>8</v>
       </c>
-      <c r="H109" s="8">
-        <v>5672</v>
+      <c r="H109" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>15</v>
@@ -5043,8 +5050,8 @@
       <c r="G110" t="s">
         <v>8</v>
       </c>
-      <c r="H110" s="8">
-        <v>5672</v>
+      <c r="H110" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>11</v>
@@ -5072,8 +5079,8 @@
       <c r="G111" t="s">
         <v>8</v>
       </c>
-      <c r="H111" s="8">
-        <v>5672</v>
+      <c r="H111" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>60</v>
@@ -5101,8 +5108,8 @@
       <c r="G112" t="s">
         <v>8</v>
       </c>
-      <c r="H112" s="8">
-        <v>5672</v>
+      <c r="H112" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>60</v>
@@ -5130,8 +5137,8 @@
       <c r="G113" t="s">
         <v>8</v>
       </c>
-      <c r="H113" s="8">
-        <v>5672</v>
+      <c r="H113" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>15</v>
@@ -5159,8 +5166,8 @@
       <c r="G114" t="s">
         <v>8</v>
       </c>
-      <c r="H114" s="8">
-        <v>5672</v>
+      <c r="H114" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>18</v>
@@ -5188,8 +5195,8 @@
       <c r="G115" t="s">
         <v>8</v>
       </c>
-      <c r="H115" s="8">
-        <v>5672</v>
+      <c r="H115" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>15</v>
@@ -5217,8 +5224,8 @@
       <c r="G116" t="s">
         <v>8</v>
       </c>
-      <c r="H116" s="8">
-        <v>5672</v>
+      <c r="H116" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>18</v>
@@ -5246,8 +5253,8 @@
       <c r="G117" t="s">
         <v>8</v>
       </c>
-      <c r="H117" s="8">
-        <v>5672</v>
+      <c r="H117" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>11</v>
@@ -5275,8 +5282,8 @@
       <c r="G118" t="s">
         <v>8</v>
       </c>
-      <c r="H118" s="8">
-        <v>5672</v>
+      <c r="H118" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>15</v>
@@ -5304,8 +5311,8 @@
       <c r="G119" t="s">
         <v>8</v>
       </c>
-      <c r="H119" s="8">
-        <v>5672</v>
+      <c r="H119" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>15</v>
@@ -5333,8 +5340,8 @@
       <c r="G120" t="s">
         <v>8</v>
       </c>
-      <c r="H120" s="8">
-        <v>5672</v>
+      <c r="H120" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>22</v>
@@ -5362,8 +5369,8 @@
       <c r="G121" t="s">
         <v>8</v>
       </c>
-      <c r="H121" s="8">
-        <v>5672</v>
+      <c r="H121" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>22</v>
@@ -5391,8 +5398,8 @@
       <c r="G122" t="s">
         <v>8</v>
       </c>
-      <c r="H122" s="8">
-        <v>5672</v>
+      <c r="H122" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>22</v>
@@ -5420,8 +5427,8 @@
       <c r="G123" t="s">
         <v>8</v>
       </c>
-      <c r="H123" s="8">
-        <v>5672</v>
+      <c r="H123" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>18</v>
@@ -5449,8 +5456,8 @@
       <c r="G124" t="s">
         <v>8</v>
       </c>
-      <c r="H124" s="8">
-        <v>5672</v>
+      <c r="H124" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>11</v>
@@ -5478,8 +5485,8 @@
       <c r="G125" t="s">
         <v>8</v>
       </c>
-      <c r="H125" s="8">
-        <v>5672</v>
+      <c r="H125" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>18</v>
@@ -5507,8 +5514,8 @@
       <c r="G126" t="s">
         <v>8</v>
       </c>
-      <c r="H126" s="8">
-        <v>5672</v>
+      <c r="H126" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>11</v>
@@ -5536,8 +5543,8 @@
       <c r="G127" t="s">
         <v>8</v>
       </c>
-      <c r="H127" s="8">
-        <v>5672</v>
+      <c r="H127" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>18</v>
@@ -5565,8 +5572,8 @@
       <c r="G128" t="s">
         <v>8</v>
       </c>
-      <c r="H128" s="8">
-        <v>5672</v>
+      <c r="H128" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>18</v>
@@ -5594,8 +5601,8 @@
       <c r="G129" t="s">
         <v>8</v>
       </c>
-      <c r="H129" s="8">
-        <v>5672</v>
+      <c r="H129" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>11</v>
@@ -5623,8 +5630,8 @@
       <c r="G130" t="s">
         <v>8</v>
       </c>
-      <c r="H130" s="8">
-        <v>5672</v>
+      <c r="H130" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>60</v>
@@ -5652,8 +5659,8 @@
       <c r="G131" t="s">
         <v>8</v>
       </c>
-      <c r="H131" s="8">
-        <v>5672</v>
+      <c r="H131" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>60</v>
@@ -5681,8 +5688,8 @@
       <c r="G132" t="s">
         <v>8</v>
       </c>
-      <c r="H132" s="8">
-        <v>5672</v>
+      <c r="H132" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>18</v>
@@ -5710,8 +5717,8 @@
       <c r="G133" t="s">
         <v>8</v>
       </c>
-      <c r="H133" s="8">
-        <v>5672</v>
+      <c r="H133" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>11</v>
@@ -5739,8 +5746,8 @@
       <c r="G134" t="s">
         <v>8</v>
       </c>
-      <c r="H134" s="8">
-        <v>5672</v>
+      <c r="H134" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>11</v>
@@ -5768,8 +5775,8 @@
       <c r="G135" t="s">
         <v>8</v>
       </c>
-      <c r="H135" s="8">
-        <v>5672</v>
+      <c r="H135" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>15</v>
@@ -5797,8 +5804,8 @@
       <c r="G136" t="s">
         <v>8</v>
       </c>
-      <c r="H136" s="8">
-        <v>5672</v>
+      <c r="H136" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>18</v>
@@ -5826,8 +5833,8 @@
       <c r="G137" t="s">
         <v>8</v>
       </c>
-      <c r="H137" s="8">
-        <v>5672</v>
+      <c r="H137" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>11</v>
@@ -5855,8 +5862,8 @@
       <c r="G138" t="s">
         <v>8</v>
       </c>
-      <c r="H138" s="8">
-        <v>5672</v>
+      <c r="H138" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>11</v>
@@ -5884,8 +5891,8 @@
       <c r="G139" t="s">
         <v>8</v>
       </c>
-      <c r="H139" s="8">
-        <v>5672</v>
+      <c r="H139" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>11</v>
@@ -5913,8 +5920,8 @@
       <c r="G140" t="s">
         <v>8</v>
       </c>
-      <c r="H140" s="8">
-        <v>5672</v>
+      <c r="H140" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>18</v>
@@ -5942,8 +5949,8 @@
       <c r="G141" t="s">
         <v>8</v>
       </c>
-      <c r="H141" s="8">
-        <v>5672</v>
+      <c r="H141" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>15</v>
@@ -5971,8 +5978,8 @@
       <c r="G142" t="s">
         <v>8</v>
       </c>
-      <c r="H142" s="8">
-        <v>5672</v>
+      <c r="H142" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>22</v>
@@ -6000,8 +6007,8 @@
       <c r="G143" t="s">
         <v>8</v>
       </c>
-      <c r="H143" s="8">
-        <v>5672</v>
+      <c r="H143" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>18</v>
@@ -6029,8 +6036,8 @@
       <c r="G144" t="s">
         <v>8</v>
       </c>
-      <c r="H144" s="8">
-        <v>5672</v>
+      <c r="H144" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>18</v>
@@ -6058,8 +6065,8 @@
       <c r="G145" t="s">
         <v>8</v>
       </c>
-      <c r="H145" s="8">
-        <v>5672</v>
+      <c r="H145" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>11</v>
@@ -6087,8 +6094,8 @@
       <c r="G146" t="s">
         <v>8</v>
       </c>
-      <c r="H146" s="8">
-        <v>5672</v>
+      <c r="H146" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>15</v>
@@ -6116,8 +6123,8 @@
       <c r="G147" t="s">
         <v>8</v>
       </c>
-      <c r="H147" s="8">
-        <v>5672</v>
+      <c r="H147" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>18</v>
@@ -6145,8 +6152,8 @@
       <c r="G148" t="s">
         <v>8</v>
       </c>
-      <c r="H148" s="8">
-        <v>5672</v>
+      <c r="H148" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>22</v>
@@ -6174,8 +6181,8 @@
       <c r="G149" t="s">
         <v>8</v>
       </c>
-      <c r="H149" s="8">
-        <v>5672</v>
+      <c r="H149" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>15</v>
@@ -6203,8 +6210,8 @@
       <c r="G150" t="s">
         <v>8</v>
       </c>
-      <c r="H150" s="8">
-        <v>5672</v>
+      <c r="H150" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I150" s="1" t="s">
         <v>22</v>
@@ -6232,8 +6239,8 @@
       <c r="G151" t="s">
         <v>8</v>
       </c>
-      <c r="H151" s="8">
-        <v>5672</v>
+      <c r="H151" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I151" s="1" t="s">
         <v>22</v>
@@ -6261,8 +6268,8 @@
       <c r="G152" t="s">
         <v>8</v>
       </c>
-      <c r="H152" s="8">
-        <v>5672</v>
+      <c r="H152" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I152" s="1" t="s">
         <v>22</v>
@@ -6290,8 +6297,8 @@
       <c r="G153" t="s">
         <v>8</v>
       </c>
-      <c r="H153" s="8">
-        <v>5672</v>
+      <c r="H153" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I153" s="1" t="s">
         <v>60</v>
@@ -6319,8 +6326,8 @@
       <c r="G154" t="s">
         <v>8</v>
       </c>
-      <c r="H154" s="8">
-        <v>5672</v>
+      <c r="H154" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>114</v>
@@ -6348,8 +6355,8 @@
       <c r="G155" t="s">
         <v>8</v>
       </c>
-      <c r="H155" s="8">
-        <v>5672</v>
+      <c r="H155" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I155" s="1" t="s">
         <v>60</v>
@@ -6377,8 +6384,8 @@
       <c r="G156" t="s">
         <v>8</v>
       </c>
-      <c r="H156" s="8">
-        <v>5672</v>
+      <c r="H156" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I156" s="1" t="s">
         <v>114</v>
@@ -6406,8 +6413,8 @@
       <c r="G157" t="s">
         <v>8</v>
       </c>
-      <c r="H157" s="8">
-        <v>5672</v>
+      <c r="H157" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I157" s="1" t="s">
         <v>60</v>
@@ -6435,8 +6442,8 @@
       <c r="G158" t="s">
         <v>8</v>
       </c>
-      <c r="H158" s="8">
-        <v>5672</v>
+      <c r="H158" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>11</v>
@@ -6464,8 +6471,8 @@
       <c r="G159" t="s">
         <v>8</v>
       </c>
-      <c r="H159" s="8">
-        <v>5672</v>
+      <c r="H159" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>22</v>
@@ -6493,8 +6500,8 @@
       <c r="G160" t="s">
         <v>8</v>
       </c>
-      <c r="H160" s="8">
-        <v>5672</v>
+      <c r="H160" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I160" s="1" t="s">
         <v>60</v>
@@ -6522,8 +6529,8 @@
       <c r="G161" t="s">
         <v>8</v>
       </c>
-      <c r="H161" s="8">
-        <v>5672</v>
+      <c r="H161" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I161" s="1" t="s">
         <v>11</v>
@@ -6551,8 +6558,8 @@
       <c r="G162" t="s">
         <v>8</v>
       </c>
-      <c r="H162" s="8">
-        <v>5672</v>
+      <c r="H162" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I162" s="1" t="s">
         <v>60</v>
@@ -6580,8 +6587,8 @@
       <c r="G163" t="s">
         <v>8</v>
       </c>
-      <c r="H163" s="8">
-        <v>5672</v>
+      <c r="H163" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I163" s="1" t="s">
         <v>18</v>
@@ -6609,8 +6616,8 @@
       <c r="G164" t="s">
         <v>8</v>
       </c>
-      <c r="H164" s="8">
-        <v>5672</v>
+      <c r="H164" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>22</v>
@@ -6638,8 +6645,8 @@
       <c r="G165" t="s">
         <v>8</v>
       </c>
-      <c r="H165" s="8">
-        <v>5672</v>
+      <c r="H165" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I165" s="1" t="s">
         <v>18</v>
@@ -6667,8 +6674,8 @@
       <c r="G166" t="s">
         <v>8</v>
       </c>
-      <c r="H166" s="8">
-        <v>5672</v>
+      <c r="H166" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>22</v>
@@ -6696,8 +6703,8 @@
       <c r="G167" t="s">
         <v>8</v>
       </c>
-      <c r="H167" s="8">
-        <v>5672</v>
+      <c r="H167" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I167" s="1" t="s">
         <v>22</v>
@@ -6725,8 +6732,8 @@
       <c r="G168" t="s">
         <v>8</v>
       </c>
-      <c r="H168" s="8">
-        <v>5672</v>
+      <c r="H168" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I168" s="1" t="s">
         <v>18</v>
@@ -6754,8 +6761,8 @@
       <c r="G169" t="s">
         <v>8</v>
       </c>
-      <c r="H169" s="8">
-        <v>5672</v>
+      <c r="H169" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>18</v>
@@ -6783,8 +6790,8 @@
       <c r="G170" t="s">
         <v>8</v>
       </c>
-      <c r="H170" s="8">
-        <v>5672</v>
+      <c r="H170" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I170" s="1" t="s">
         <v>15</v>
@@ -6812,8 +6819,8 @@
       <c r="G171" t="s">
         <v>8</v>
       </c>
-      <c r="H171" s="8">
-        <v>5672</v>
+      <c r="H171" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I171" s="1" t="s">
         <v>15</v>
@@ -6841,8 +6848,8 @@
       <c r="G172" t="s">
         <v>8</v>
       </c>
-      <c r="H172" s="8">
-        <v>5672</v>
+      <c r="H172" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I172" s="1" t="s">
         <v>22</v>
@@ -6870,8 +6877,8 @@
       <c r="G173" t="s">
         <v>8</v>
       </c>
-      <c r="H173" s="8">
-        <v>5672</v>
+      <c r="H173" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I173" s="1" t="s">
         <v>11</v>
@@ -6899,8 +6906,8 @@
       <c r="G174" t="s">
         <v>8</v>
       </c>
-      <c r="H174" s="8">
-        <v>5672</v>
+      <c r="H174" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I174" s="1" t="s">
         <v>11</v>
@@ -6928,8 +6935,8 @@
       <c r="G175" t="s">
         <v>8</v>
       </c>
-      <c r="H175" s="8">
-        <v>5672</v>
+      <c r="H175" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I175" s="1" t="s">
         <v>15</v>
@@ -6957,8 +6964,8 @@
       <c r="G176" t="s">
         <v>8</v>
       </c>
-      <c r="H176" s="8">
-        <v>5672</v>
+      <c r="H176" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I176" s="1" t="s">
         <v>15</v>
@@ -6986,8 +6993,8 @@
       <c r="G177" t="s">
         <v>8</v>
       </c>
-      <c r="H177" s="8">
-        <v>5672</v>
+      <c r="H177" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I177" s="1" t="s">
         <v>15</v>
@@ -7015,8 +7022,8 @@
       <c r="G178" t="s">
         <v>8</v>
       </c>
-      <c r="H178" s="8">
-        <v>5672</v>
+      <c r="H178" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I178" s="1" t="s">
         <v>18</v>
@@ -7044,8 +7051,8 @@
       <c r="G179" t="s">
         <v>8</v>
       </c>
-      <c r="H179" s="8">
-        <v>5672</v>
+      <c r="H179" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I179" s="1" t="s">
         <v>15</v>
@@ -7073,8 +7080,8 @@
       <c r="G180" t="s">
         <v>8</v>
       </c>
-      <c r="H180" s="8">
-        <v>5672</v>
+      <c r="H180" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I180" s="1" t="s">
         <v>15</v>
@@ -7102,8 +7109,8 @@
       <c r="G181" t="s">
         <v>8</v>
       </c>
-      <c r="H181" s="8">
-        <v>5672</v>
+      <c r="H181" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I181" s="1" t="s">
         <v>60</v>
@@ -7131,8 +7138,8 @@
       <c r="G182" t="s">
         <v>8</v>
       </c>
-      <c r="H182" s="8">
-        <v>5672</v>
+      <c r="H182" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>18</v>
@@ -7160,8 +7167,8 @@
       <c r="G183" t="s">
         <v>8</v>
       </c>
-      <c r="H183" s="8">
-        <v>5672</v>
+      <c r="H183" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I183" s="1" t="s">
         <v>11</v>
@@ -7189,8 +7196,8 @@
       <c r="G184" t="s">
         <v>8</v>
       </c>
-      <c r="H184" s="8">
-        <v>5672</v>
+      <c r="H184" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I184" s="1" t="s">
         <v>11</v>
@@ -7218,8 +7225,8 @@
       <c r="G185" t="s">
         <v>8</v>
       </c>
-      <c r="H185" s="8">
-        <v>5672</v>
+      <c r="H185" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>11</v>
@@ -7247,8 +7254,8 @@
       <c r="G186" t="s">
         <v>8</v>
       </c>
-      <c r="H186" s="8">
-        <v>5672</v>
+      <c r="H186" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I186" s="1" t="s">
         <v>22</v>
@@ -7276,8 +7283,8 @@
       <c r="G187" t="s">
         <v>8</v>
       </c>
-      <c r="H187" s="8">
-        <v>5672</v>
+      <c r="H187" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I187" s="1" t="s">
         <v>11</v>
@@ -7305,8 +7312,8 @@
       <c r="G188" t="s">
         <v>8</v>
       </c>
-      <c r="H188" s="8">
-        <v>5672</v>
+      <c r="H188" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I188" s="1" t="s">
         <v>11</v>
@@ -7334,8 +7341,8 @@
       <c r="G189" t="s">
         <v>8</v>
       </c>
-      <c r="H189" s="8">
-        <v>5672</v>
+      <c r="H189" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I189" s="1" t="s">
         <v>11</v>
@@ -7363,8 +7370,8 @@
       <c r="G190" t="s">
         <v>8</v>
       </c>
-      <c r="H190" s="8">
-        <v>5672</v>
+      <c r="H190" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I190" s="1" t="s">
         <v>11</v>
@@ -7392,8 +7399,8 @@
       <c r="G191" t="s">
         <v>8</v>
       </c>
-      <c r="H191" s="8">
-        <v>5672</v>
+      <c r="H191" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I191" s="1" t="s">
         <v>11</v>
@@ -7421,8 +7428,8 @@
       <c r="G192" t="s">
         <v>8</v>
       </c>
-      <c r="H192" s="8">
-        <v>5672</v>
+      <c r="H192" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I192" s="1" t="s">
         <v>11</v>
@@ -7450,8 +7457,8 @@
       <c r="G193" t="s">
         <v>8</v>
       </c>
-      <c r="H193" s="8">
-        <v>5672</v>
+      <c r="H193" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I193" s="1" t="s">
         <v>11</v>
@@ -7479,8 +7486,8 @@
       <c r="G194" t="s">
         <v>8</v>
       </c>
-      <c r="H194" s="8">
-        <v>5672</v>
+      <c r="H194" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I194" s="1" t="s">
         <v>11</v>
@@ -7508,8 +7515,8 @@
       <c r="G195" t="s">
         <v>8</v>
       </c>
-      <c r="H195" s="8">
-        <v>5672</v>
+      <c r="H195" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I195" s="1" t="s">
         <v>11</v>
@@ -7537,8 +7544,8 @@
       <c r="G196" t="s">
         <v>8</v>
       </c>
-      <c r="H196" s="8">
-        <v>5672</v>
+      <c r="H196" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I196" s="1" t="s">
         <v>11</v>
@@ -7566,8 +7573,8 @@
       <c r="G197" t="s">
         <v>8</v>
       </c>
-      <c r="H197" s="8">
-        <v>5672</v>
+      <c r="H197" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I197" s="1" t="s">
         <v>11</v>
@@ -7595,8 +7602,8 @@
       <c r="G198" t="s">
         <v>8</v>
       </c>
-      <c r="H198" s="8">
-        <v>5672</v>
+      <c r="H198" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I198" s="1" t="s">
         <v>11</v>
@@ -7624,8 +7631,8 @@
       <c r="G199" t="s">
         <v>8</v>
       </c>
-      <c r="H199" s="8">
-        <v>5672</v>
+      <c r="H199" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I199" s="1" t="s">
         <v>11</v>
@@ -7653,8 +7660,8 @@
       <c r="G200" t="s">
         <v>8</v>
       </c>
-      <c r="H200" s="8">
-        <v>5672</v>
+      <c r="H200" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I200" s="1" t="s">
         <v>11</v>
@@ -7682,8 +7689,8 @@
       <c r="G201" t="s">
         <v>8</v>
       </c>
-      <c r="H201" s="8">
-        <v>5672</v>
+      <c r="H201" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I201" s="1" t="s">
         <v>11</v>
@@ -7711,8 +7718,8 @@
       <c r="G202" t="s">
         <v>8</v>
       </c>
-      <c r="H202" s="8">
-        <v>5672</v>
+      <c r="H202" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I202" s="1" t="s">
         <v>11</v>
@@ -7740,8 +7747,8 @@
       <c r="G203" t="s">
         <v>8</v>
       </c>
-      <c r="H203" s="8">
-        <v>5672</v>
+      <c r="H203" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I203" s="1" t="s">
         <v>11</v>
@@ -7769,8 +7776,8 @@
       <c r="G204" t="s">
         <v>8</v>
       </c>
-      <c r="H204" s="8">
-        <v>5672</v>
+      <c r="H204" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I204" s="1" t="s">
         <v>22</v>
@@ -7798,8 +7805,8 @@
       <c r="G205" t="s">
         <v>8</v>
       </c>
-      <c r="H205" s="8">
-        <v>5672</v>
+      <c r="H205" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I205" s="1" t="s">
         <v>11</v>
@@ -7827,8 +7834,8 @@
       <c r="G206" t="s">
         <v>8</v>
       </c>
-      <c r="H206" s="8">
-        <v>5672</v>
+      <c r="H206" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I206" s="1" t="s">
         <v>11</v>
@@ -7856,8 +7863,8 @@
       <c r="G207" t="s">
         <v>8</v>
       </c>
-      <c r="H207" s="8">
-        <v>5672</v>
+      <c r="H207" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I207" s="1" t="s">
         <v>128</v>
@@ -7885,8 +7892,8 @@
       <c r="G208" t="s">
         <v>8</v>
       </c>
-      <c r="H208" s="8">
-        <v>5672</v>
+      <c r="H208" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I208" s="1" t="s">
         <v>11</v>
@@ -7914,8 +7921,8 @@
       <c r="G209" t="s">
         <v>8</v>
       </c>
-      <c r="H209" s="8">
-        <v>5672</v>
+      <c r="H209" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I209" s="1" t="s">
         <v>15</v>
@@ -7943,8 +7950,8 @@
       <c r="G210" t="s">
         <v>8</v>
       </c>
-      <c r="H210" s="8">
-        <v>5672</v>
+      <c r="H210" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I210" s="1" t="s">
         <v>18</v>
@@ -7972,8 +7979,8 @@
       <c r="G211" t="s">
         <v>8</v>
       </c>
-      <c r="H211" s="8">
-        <v>5672</v>
+      <c r="H211" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I211" s="1" t="s">
         <v>60</v>
@@ -8001,8 +8008,8 @@
       <c r="G212" t="s">
         <v>8</v>
       </c>
-      <c r="H212" s="8">
-        <v>5672</v>
+      <c r="H212" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>60</v>
@@ -8030,8 +8037,8 @@
       <c r="G213" t="s">
         <v>8</v>
       </c>
-      <c r="H213" s="8">
-        <v>5672</v>
+      <c r="H213" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I213" s="1" t="s">
         <v>11</v>
@@ -8059,8 +8066,8 @@
       <c r="G214" t="s">
         <v>8</v>
       </c>
-      <c r="H214" s="8">
-        <v>5672</v>
+      <c r="H214" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I214" s="1" t="s">
         <v>11</v>
@@ -8088,8 +8095,8 @@
       <c r="G215" t="s">
         <v>8</v>
       </c>
-      <c r="H215" s="8">
-        <v>5672</v>
+      <c r="H215" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I215" s="1" t="s">
         <v>15</v>
@@ -8117,8 +8124,8 @@
       <c r="G216" t="s">
         <v>8</v>
       </c>
-      <c r="H216" s="8">
-        <v>5672</v>
+      <c r="H216" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>60</v>
@@ -8146,8 +8153,8 @@
       <c r="G217" t="s">
         <v>8</v>
       </c>
-      <c r="H217" s="8">
-        <v>5672</v>
+      <c r="H217" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I217" s="1" t="s">
         <v>15</v>
@@ -8175,8 +8182,8 @@
       <c r="G218" t="s">
         <v>8</v>
       </c>
-      <c r="H218" s="8">
-        <v>5672</v>
+      <c r="H218" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>15</v>
@@ -8204,8 +8211,8 @@
       <c r="G219" t="s">
         <v>8</v>
       </c>
-      <c r="H219" s="8">
-        <v>5672</v>
+      <c r="H219" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>15</v>
@@ -8233,8 +8240,8 @@
       <c r="G220" t="s">
         <v>8</v>
       </c>
-      <c r="H220" s="8">
-        <v>5672</v>
+      <c r="H220" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I220" s="1" t="s">
         <v>15</v>
@@ -8245,7 +8252,7 @@
         <v>5</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>29</v>
+        <v>312</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>7</v>
@@ -8257,13 +8264,13 @@
         <v>316</v>
       </c>
       <c r="F221" t="s">
-        <v>102</v>
+        <v>33</v>
       </c>
       <c r="G221" t="s">
         <v>8</v>
       </c>
-      <c r="H221" s="8">
-        <v>5672</v>
+      <c r="H221" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I221" s="1" t="s">
         <v>60</v>
@@ -8271,10 +8278,10 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A222" s="3" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>317</v>
+        <v>29</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>7</v>
@@ -8283,16 +8290,16 @@
         <v>8</v>
       </c>
       <c r="E222" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F222" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="G222" t="s">
         <v>8</v>
       </c>
-      <c r="H222" s="8">
-        <v>5672</v>
+      <c r="H222" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I222" s="1" t="s">
         <v>60</v>
@@ -8300,10 +8307,10 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A223" s="3" t="s">
-        <v>319</v>
+        <v>5</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>16</v>
+        <v>317</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>7</v>
@@ -8312,27 +8319,27 @@
         <v>8</v>
       </c>
       <c r="E223" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F223" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="G223" t="s">
         <v>8</v>
       </c>
-      <c r="H223" s="8">
-        <v>5672</v>
+      <c r="H223" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I223" s="1" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A224" s="3" t="s">
-        <v>5</v>
+        <v>319</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>7</v>
@@ -8341,27 +8348,27 @@
         <v>8</v>
       </c>
       <c r="E224" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F224" t="s">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="G224" t="s">
         <v>8</v>
       </c>
-      <c r="H224" s="8">
-        <v>5672</v>
+      <c r="H224" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I224" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A225" s="3" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>164</v>
+        <v>6</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>7</v>
@@ -8370,24 +8377,24 @@
         <v>8</v>
       </c>
       <c r="E225" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F225" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G225" t="s">
         <v>8</v>
       </c>
-      <c r="H225" s="8">
-        <v>5672</v>
+      <c r="H225" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I225" s="1" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A226" s="3" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="B226" s="3" t="s">
         <v>164</v>
@@ -8399,7 +8406,7 @@
         <v>8</v>
       </c>
       <c r="E226" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F226" t="s">
         <v>14</v>
@@ -8407,11 +8414,11 @@
       <c r="G226" t="s">
         <v>8</v>
       </c>
-      <c r="H226" s="8">
-        <v>5672</v>
+      <c r="H226" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I226" s="1" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.35">
@@ -8419,7 +8426,7 @@
         <v>5</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>6</v>
+        <v>164</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>7</v>
@@ -8428,16 +8435,16 @@
         <v>8</v>
       </c>
       <c r="E227" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F227" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G227" t="s">
         <v>8</v>
       </c>
-      <c r="H227" s="8">
-        <v>5672</v>
+      <c r="H227" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I227" s="1" t="s">
         <v>18</v>
@@ -8445,10 +8452,10 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A228" s="3" t="s">
-        <v>325</v>
+        <v>5</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>325</v>
+        <v>6</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>7</v>
@@ -8457,7 +8464,7 @@
         <v>8</v>
       </c>
       <c r="E228" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F228" t="s">
         <v>33</v>
@@ -8465,19 +8472,19 @@
       <c r="G228" t="s">
         <v>8</v>
       </c>
-      <c r="H228" s="8">
-        <v>5672</v>
+      <c r="H228" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I228" s="1" t="s">
-        <v>128</v>
+        <v>18</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A229" s="3" t="s">
-        <v>28</v>
+        <v>325</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>16</v>
+        <v>325</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>7</v>
@@ -8486,27 +8493,27 @@
         <v>8</v>
       </c>
       <c r="E229" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F229" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G229" t="s">
         <v>8</v>
       </c>
-      <c r="H229" s="8">
-        <v>5672</v>
+      <c r="H229" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>11</v>
+        <v>128</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A230" s="3" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>7</v>
@@ -8515,27 +8522,27 @@
         <v>8</v>
       </c>
       <c r="E230" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F230" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G230" t="s">
         <v>8</v>
       </c>
-      <c r="H230" s="8">
-        <v>5672</v>
+      <c r="H230" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A231" s="3" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>7</v>
@@ -8547,13 +8554,13 @@
         <v>328</v>
       </c>
       <c r="F231" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G231" t="s">
         <v>8</v>
       </c>
-      <c r="H231" s="8">
-        <v>5672</v>
+      <c r="H231" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I231" s="1" t="s">
         <v>15</v>
@@ -8561,10 +8568,10 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A232" s="3" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>7</v>
@@ -8573,16 +8580,16 @@
         <v>8</v>
       </c>
       <c r="E232" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F232" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G232" t="s">
-        <v>180</v>
-      </c>
-      <c r="H232" s="8">
-        <v>5672</v>
+        <v>8</v>
+      </c>
+      <c r="H232" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I232" s="1" t="s">
         <v>15</v>
@@ -8590,10 +8597,10 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A233" s="3" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>126</v>
+        <v>26</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>7</v>
@@ -8602,27 +8609,27 @@
         <v>8</v>
       </c>
       <c r="E233" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F233" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G233" t="s">
         <v>8</v>
       </c>
-      <c r="H233" s="8">
-        <v>5672</v>
+      <c r="H233" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I233" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A234" s="3" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>6</v>
+        <v>126</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>7</v>
@@ -8634,24 +8641,24 @@
         <v>330</v>
       </c>
       <c r="F234" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G234" t="s">
         <v>8</v>
       </c>
-      <c r="H234" s="8">
-        <v>5672</v>
+      <c r="H234" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I234" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A235" s="3" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>147</v>
+        <v>6</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>7</v>
@@ -8663,24 +8670,24 @@
         <v>330</v>
       </c>
       <c r="F235" t="s">
-        <v>102</v>
+        <v>33</v>
       </c>
       <c r="G235" t="s">
         <v>8</v>
       </c>
-      <c r="H235" s="8">
-        <v>5672</v>
+      <c r="H235" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I235" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A236" s="3" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>28</v>
+        <v>147</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>7</v>
@@ -8689,16 +8696,16 @@
         <v>8</v>
       </c>
       <c r="E236" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F236" t="s">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="G236" t="s">
         <v>8</v>
       </c>
-      <c r="H236" s="8">
-        <v>5672</v>
+      <c r="H236" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I236" s="1" t="s">
         <v>22</v>
@@ -8706,10 +8713,10 @@
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A237" s="3" t="s">
-        <v>332</v>
+        <v>5</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>333</v>
+        <v>28</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>7</v>
@@ -8718,27 +8725,27 @@
         <v>8</v>
       </c>
       <c r="E237" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F237" t="s">
-        <v>102</v>
+        <v>33</v>
       </c>
       <c r="G237" t="s">
         <v>8</v>
       </c>
-      <c r="H237" s="8">
-        <v>5672</v>
+      <c r="H237" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I237" s="1" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A238" s="3" t="s">
-        <v>94</v>
+        <v>332</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>7</v>
@@ -8747,27 +8754,27 @@
         <v>8</v>
       </c>
       <c r="E238" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F238" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="G238" t="s">
         <v>8</v>
       </c>
-      <c r="H238" s="8">
-        <v>5672</v>
+      <c r="H238" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I238" s="1" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A239" s="3" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>39</v>
+        <v>335</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>7</v>
@@ -8776,7 +8783,7 @@
         <v>8</v>
       </c>
       <c r="E239" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F239" t="s">
         <v>14</v>
@@ -8784,19 +8791,19 @@
       <c r="G239" t="s">
         <v>8</v>
       </c>
-      <c r="H239" s="8">
-        <v>5672</v>
+      <c r="H239" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I239" s="1" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A240" s="3" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>7</v>
@@ -8805,7 +8812,7 @@
         <v>8</v>
       </c>
       <c r="E240" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F240" t="s">
         <v>14</v>
@@ -8813,19 +8820,19 @@
       <c r="G240" t="s">
         <v>8</v>
       </c>
-      <c r="H240" s="8">
-        <v>5672</v>
+      <c r="H240" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I240" s="1" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A241" s="3" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>7</v>
@@ -8834,19 +8841,19 @@
         <v>8</v>
       </c>
       <c r="E241" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F241" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G241" t="s">
         <v>8</v>
       </c>
-      <c r="H241" s="8">
-        <v>5672</v>
+      <c r="H241" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I241" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.35">
@@ -8854,7 +8861,7 @@
         <v>5</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>7</v>
@@ -8863,19 +8870,19 @@
         <v>8</v>
       </c>
       <c r="E242" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F242" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G242" t="s">
         <v>8</v>
       </c>
-      <c r="H242" s="8">
-        <v>5672</v>
+      <c r="H242" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I242" s="1" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.35">
@@ -8883,28 +8890,28 @@
         <v>5</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D243" t="s">
-        <v>341</v>
+        <v>8</v>
       </c>
       <c r="E243" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F243" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G243" t="s">
         <v>8</v>
       </c>
-      <c r="H243" s="8">
-        <v>5672</v>
+      <c r="H243" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I243" s="1" t="s">
-        <v>11</v>
+        <v>60</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.35">
@@ -8912,13 +8919,13 @@
         <v>5</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D244" t="s">
-        <v>72</v>
+        <v>341</v>
       </c>
       <c r="E244" t="s">
         <v>342</v>
@@ -8929,8 +8936,8 @@
       <c r="G244" t="s">
         <v>8</v>
       </c>
-      <c r="H244" s="8">
-        <v>5672</v>
+      <c r="H244" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I244" s="1" t="s">
         <v>11</v>
@@ -8941,16 +8948,16 @@
         <v>5</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D245" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="E245" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F245" t="s">
         <v>14</v>
@@ -8958,22 +8965,22 @@
       <c r="G245" t="s">
         <v>8</v>
       </c>
-      <c r="H245" s="8">
-        <v>5672</v>
+      <c r="H245" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I245" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A246" s="3" t="s">
-        <v>344</v>
+        <v>5</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>345</v>
+        <v>26</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="D246" t="s">
         <v>8</v>
@@ -8987,22 +8994,22 @@
       <c r="G246" t="s">
         <v>8</v>
       </c>
-      <c r="H246" s="8">
-        <v>5672</v>
+      <c r="H246" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I246" s="1" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A247" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>31</v>
+        <v>345</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D247" t="s">
         <v>8</v>
@@ -9016,22 +9023,22 @@
       <c r="G247" t="s">
         <v>8</v>
       </c>
-      <c r="H247" s="8">
-        <v>5672</v>
+      <c r="H247" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I247" s="1" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A248" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>348</v>
+        <v>31</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D248" t="s">
         <v>8</v>
@@ -9045,8 +9052,8 @@
       <c r="G248" t="s">
         <v>8</v>
       </c>
-      <c r="H248" s="8">
-        <v>5672</v>
+      <c r="H248" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I248" s="1" t="s">
         <v>22</v>
@@ -9054,19 +9061,19 @@
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A249" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="D249" t="s">
         <v>8</v>
       </c>
       <c r="E249" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F249" t="s">
         <v>14</v>
@@ -9074,19 +9081,19 @@
       <c r="G249" t="s">
         <v>8</v>
       </c>
-      <c r="H249" s="8">
-        <v>5672</v>
+      <c r="H249" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I249" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A250" s="3" t="s">
-        <v>5</v>
+        <v>349</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>29</v>
+        <v>350</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>7</v>
@@ -9095,19 +9102,19 @@
         <v>8</v>
       </c>
       <c r="E250" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F250" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G250" t="s">
         <v>8</v>
       </c>
-      <c r="H250" s="8">
-        <v>5672</v>
+      <c r="H250" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I250" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.35">
@@ -9124,7 +9131,7 @@
         <v>8</v>
       </c>
       <c r="E251" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F251" t="s">
         <v>33</v>
@@ -9132,11 +9139,11 @@
       <c r="G251" t="s">
         <v>8</v>
       </c>
-      <c r="H251" s="8">
-        <v>5672</v>
+      <c r="H251" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.35">
@@ -9144,7 +9151,7 @@
         <v>5</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>7</v>
@@ -9153,7 +9160,7 @@
         <v>8</v>
       </c>
       <c r="E252" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F252" t="s">
         <v>33</v>
@@ -9161,11 +9168,11 @@
       <c r="G252" t="s">
         <v>8</v>
       </c>
-      <c r="H252" s="8">
-        <v>5672</v>
+      <c r="H252" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I252" s="1" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.35">
@@ -9173,7 +9180,7 @@
         <v>5</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>7</v>
@@ -9182,7 +9189,7 @@
         <v>8</v>
       </c>
       <c r="E253" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F253" t="s">
         <v>33</v>
@@ -9190,8 +9197,8 @@
       <c r="G253" t="s">
         <v>8</v>
       </c>
-      <c r="H253" s="8">
-        <v>5672</v>
+      <c r="H253" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I253" s="1" t="s">
         <v>22</v>
@@ -9202,7 +9209,7 @@
         <v>5</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>7</v>
@@ -9211,7 +9218,7 @@
         <v>8</v>
       </c>
       <c r="E254" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F254" t="s">
         <v>33</v>
@@ -9219,11 +9226,11 @@
       <c r="G254" t="s">
         <v>8</v>
       </c>
-      <c r="H254" s="8">
-        <v>5672</v>
+      <c r="H254" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I254" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.35">
@@ -9231,7 +9238,7 @@
         <v>5</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>357</v>
+        <v>6</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>7</v>
@@ -9240,19 +9247,19 @@
         <v>8</v>
       </c>
       <c r="E255" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F255" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G255" t="s">
         <v>8</v>
       </c>
-      <c r="H255" s="8">
-        <v>5672</v>
+      <c r="H255" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I255" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.35">
@@ -9260,7 +9267,7 @@
         <v>5</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>23</v>
+        <v>357</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>7</v>
@@ -9269,7 +9276,7 @@
         <v>8</v>
       </c>
       <c r="E256" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F256" t="s">
         <v>14</v>
@@ -9277,8 +9284,8 @@
       <c r="G256" t="s">
         <v>8</v>
       </c>
-      <c r="H256" s="8">
-        <v>5672</v>
+      <c r="H256" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I256" s="1" t="s">
         <v>18</v>
@@ -9289,7 +9296,7 @@
         <v>5</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>7</v>
@@ -9298,7 +9305,7 @@
         <v>8</v>
       </c>
       <c r="E257" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F257" t="s">
         <v>14</v>
@@ -9306,8 +9313,8 @@
       <c r="G257" t="s">
         <v>8</v>
       </c>
-      <c r="H257" s="8">
-        <v>5672</v>
+      <c r="H257" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I257" s="1" t="s">
         <v>18</v>
@@ -9321,36 +9328,36 @@
         <v>6</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="D258" t="s">
         <v>8</v>
       </c>
       <c r="E258" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F258" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="G258" t="s">
         <v>8</v>
       </c>
-      <c r="H258" s="8">
-        <v>5672</v>
+      <c r="H258" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I258" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A259" s="3" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D259" t="s">
         <v>8</v>
@@ -9364,8 +9371,8 @@
       <c r="G259" t="s">
         <v>8</v>
       </c>
-      <c r="H259" s="8">
-        <v>5672</v>
+      <c r="H259" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I259" s="1" t="s">
         <v>22</v>
@@ -9373,13 +9380,13 @@
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A260" s="3" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D260" t="s">
         <v>8</v>
@@ -9393,22 +9400,22 @@
       <c r="G260" t="s">
         <v>8</v>
       </c>
-      <c r="H260" s="8">
-        <v>5672</v>
+      <c r="H260" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I260" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A261" s="3" t="s">
-        <v>202</v>
+        <v>61</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="D261" t="s">
         <v>8</v>
@@ -9422,19 +9429,19 @@
       <c r="G261" t="s">
         <v>8</v>
       </c>
-      <c r="H261" s="8">
-        <v>5672</v>
+      <c r="H261" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I261" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A262" s="3" t="s">
-        <v>5</v>
+        <v>202</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>7</v>
@@ -9443,19 +9450,19 @@
         <v>8</v>
       </c>
       <c r="E262" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F262" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="G262" t="s">
         <v>8</v>
       </c>
-      <c r="H262" s="8">
-        <v>5672</v>
+      <c r="H262" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I262" s="1" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.35">
@@ -9463,7 +9470,7 @@
         <v>5</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>7</v>
@@ -9472,19 +9479,19 @@
         <v>8</v>
       </c>
       <c r="E263" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F263" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G263" t="s">
         <v>8</v>
       </c>
-      <c r="H263" s="8">
-        <v>5672</v>
+      <c r="H263" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I263" s="1" t="s">
-        <v>11</v>
+        <v>60</v>
       </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.35">
@@ -9492,7 +9499,7 @@
         <v>5</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>7</v>
@@ -9501,19 +9508,19 @@
         <v>8</v>
       </c>
       <c r="E264" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F264" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G264" t="s">
         <v>8</v>
       </c>
-      <c r="H264" s="8">
-        <v>5672</v>
+      <c r="H264" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I264" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.35">
@@ -9521,13 +9528,13 @@
         <v>5</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D265" t="s">
-        <v>341</v>
+        <v>8</v>
       </c>
       <c r="E265" t="s">
         <v>364</v>
@@ -9538,8 +9545,8 @@
       <c r="G265" t="s">
         <v>8</v>
       </c>
-      <c r="H265" s="8">
-        <v>5672</v>
+      <c r="H265" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I265" s="1" t="s">
         <v>22</v>
@@ -9550,13 +9557,13 @@
         <v>5</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D266" t="s">
-        <v>72</v>
+        <v>341</v>
       </c>
       <c r="E266" t="s">
         <v>364</v>
@@ -9567,8 +9574,8 @@
       <c r="G266" t="s">
         <v>8</v>
       </c>
-      <c r="H266" s="8">
-        <v>5672</v>
+      <c r="H266" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I266" s="1" t="s">
         <v>22</v>
@@ -9576,39 +9583,39 @@
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A267" s="3" t="s">
-        <v>365</v>
+        <v>5</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>366</v>
+        <v>39</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D267" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="E267" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="F267" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G267" t="s">
         <v>8</v>
       </c>
-      <c r="H267" s="8">
-        <v>5672</v>
+      <c r="H267" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I267" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A268" s="3" t="s">
-        <v>5</v>
+        <v>365</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>104</v>
+        <v>366</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>7</v>
@@ -9617,27 +9624,27 @@
         <v>8</v>
       </c>
       <c r="E268" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F268" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G268" t="s">
         <v>8</v>
       </c>
-      <c r="H268" s="8">
-        <v>5672</v>
+      <c r="H268" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I268" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A269" s="3" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>160</v>
+        <v>104</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>7</v>
@@ -9649,13 +9656,13 @@
         <v>368</v>
       </c>
       <c r="F269" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="G269" t="s">
         <v>8</v>
       </c>
-      <c r="H269" s="8">
-        <v>5672</v>
+      <c r="H269" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I269" s="1" t="s">
         <v>18</v>
@@ -9663,10 +9670,10 @@
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A270" s="3" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>369</v>
+        <v>160</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>7</v>
@@ -9675,19 +9682,19 @@
         <v>8</v>
       </c>
       <c r="E270" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F270" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="G270" t="s">
         <v>8</v>
       </c>
-      <c r="H270" s="8">
-        <v>5672</v>
+      <c r="H270" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I270" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.35">
@@ -9695,7 +9702,7 @@
         <v>5</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>23</v>
+        <v>369</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>7</v>
@@ -9704,7 +9711,7 @@
         <v>8</v>
       </c>
       <c r="E271" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F271" t="s">
         <v>33</v>
@@ -9712,8 +9719,8 @@
       <c r="G271" t="s">
         <v>8</v>
       </c>
-      <c r="H271" s="8">
-        <v>5672</v>
+      <c r="H271" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I271" s="1" t="s">
         <v>11</v>
@@ -9724,7 +9731,7 @@
         <v>5</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>7</v>
@@ -9733,19 +9740,19 @@
         <v>8</v>
       </c>
       <c r="E272" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F272" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G272" t="s">
         <v>8</v>
       </c>
-      <c r="H272" s="8">
-        <v>5672</v>
+      <c r="H272" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I272" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.35">
@@ -9753,7 +9760,7 @@
         <v>5</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>7</v>
@@ -9762,16 +9769,16 @@
         <v>8</v>
       </c>
       <c r="E273" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F273" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G273" t="s">
         <v>8</v>
       </c>
-      <c r="H273" s="8">
-        <v>5672</v>
+      <c r="H273" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I273" s="1" t="s">
         <v>15</v>
@@ -9782,7 +9789,7 @@
         <v>5</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>7</v>
@@ -9791,16 +9798,16 @@
         <v>8</v>
       </c>
       <c r="E274" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F274" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G274" t="s">
         <v>8</v>
       </c>
-      <c r="H274" s="8">
-        <v>5672</v>
+      <c r="H274" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I274" s="1" t="s">
         <v>15</v>
@@ -9820,7 +9827,7 @@
         <v>8</v>
       </c>
       <c r="E275" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F275" t="s">
         <v>33</v>
@@ -9828,11 +9835,11 @@
       <c r="G275" t="s">
         <v>8</v>
       </c>
-      <c r="H275" s="8">
-        <v>5672</v>
+      <c r="H275" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I275" s="1" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.35">
@@ -9840,7 +9847,7 @@
         <v>5</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>7</v>
@@ -9849,16 +9856,16 @@
         <v>8</v>
       </c>
       <c r="E276" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F276" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G276" t="s">
         <v>8</v>
       </c>
-      <c r="H276" s="8">
-        <v>5672</v>
+      <c r="H276" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I276" s="1" t="s">
         <v>60</v>
@@ -9866,7 +9873,7 @@
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A277" s="3" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="B277" s="3" t="s">
         <v>29</v>
@@ -9878,27 +9885,27 @@
         <v>8</v>
       </c>
       <c r="E277" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F277" t="s">
-        <v>378</v>
+        <v>14</v>
       </c>
       <c r="G277" t="s">
         <v>8</v>
       </c>
-      <c r="H277" s="8">
-        <v>5672</v>
+      <c r="H277" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I277" s="1" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A278" s="3" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>7</v>
@@ -9907,19 +9914,19 @@
         <v>8</v>
       </c>
       <c r="E278" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F278" t="s">
-        <v>14</v>
+        <v>378</v>
       </c>
       <c r="G278" t="s">
         <v>8</v>
       </c>
-      <c r="H278" s="8">
-        <v>5672</v>
+      <c r="H278" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I278" s="1" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.35">
@@ -9927,7 +9934,7 @@
         <v>5</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>7</v>
@@ -9936,7 +9943,7 @@
         <v>8</v>
       </c>
       <c r="E279" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F279" t="s">
         <v>14</v>
@@ -9944,11 +9951,11 @@
       <c r="G279" t="s">
         <v>8</v>
       </c>
-      <c r="H279" s="8">
-        <v>5672</v>
+      <c r="H279" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I279" s="1" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.35">
@@ -9956,7 +9963,7 @@
         <v>5</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>7</v>
@@ -9965,7 +9972,7 @@
         <v>8</v>
       </c>
       <c r="E280" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F280" t="s">
         <v>14</v>
@@ -9973,11 +9980,11 @@
       <c r="G280" t="s">
         <v>8</v>
       </c>
-      <c r="H280" s="8">
-        <v>5672</v>
+      <c r="H280" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I280" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.35">
@@ -9985,7 +9992,7 @@
         <v>5</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>382</v>
+        <v>16</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>7</v>
@@ -9994,7 +10001,7 @@
         <v>8</v>
       </c>
       <c r="E281" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F281" t="s">
         <v>14</v>
@@ -10002,8 +10009,8 @@
       <c r="G281" t="s">
         <v>8</v>
       </c>
-      <c r="H281" s="8">
-        <v>5672</v>
+      <c r="H281" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I281" s="1" t="s">
         <v>11</v>
@@ -10014,7 +10021,7 @@
         <v>5</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>348</v>
+        <v>382</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>7</v>
@@ -10023,7 +10030,7 @@
         <v>8</v>
       </c>
       <c r="E282" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F282" t="s">
         <v>14</v>
@@ -10031,11 +10038,11 @@
       <c r="G282" t="s">
         <v>8</v>
       </c>
-      <c r="H282" s="8">
-        <v>5672</v>
+      <c r="H282" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I282" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.35">
@@ -10043,7 +10050,7 @@
         <v>5</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>6</v>
+        <v>348</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>7</v>
@@ -10052,16 +10059,16 @@
         <v>8</v>
       </c>
       <c r="E283" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F283" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G283" t="s">
         <v>8</v>
       </c>
-      <c r="H283" s="8">
-        <v>5672</v>
+      <c r="H283" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I283" s="1" t="s">
         <v>18</v>
@@ -10072,7 +10079,7 @@
         <v>5</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>7</v>
@@ -10081,16 +10088,16 @@
         <v>8</v>
       </c>
       <c r="E284" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F284" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G284" t="s">
         <v>8</v>
       </c>
-      <c r="H284" s="8">
-        <v>5672</v>
+      <c r="H284" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I284" s="1" t="s">
         <v>18</v>
@@ -10101,7 +10108,7 @@
         <v>5</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>387</v>
+        <v>51</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>7</v>
@@ -10110,7 +10117,7 @@
         <v>8</v>
       </c>
       <c r="E285" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F285" t="s">
         <v>14</v>
@@ -10118,8 +10125,8 @@
       <c r="G285" t="s">
         <v>8</v>
       </c>
-      <c r="H285" s="8">
-        <v>5672</v>
+      <c r="H285" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I285" s="1" t="s">
         <v>18</v>
@@ -10127,10 +10134,10 @@
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A286" s="3" t="s">
-        <v>277</v>
+        <v>5</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>7</v>
@@ -10139,7 +10146,7 @@
         <v>8</v>
       </c>
       <c r="E286" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F286" t="s">
         <v>14</v>
@@ -10147,8 +10154,8 @@
       <c r="G286" t="s">
         <v>8</v>
       </c>
-      <c r="H286" s="8">
-        <v>5672</v>
+      <c r="H286" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I286" s="1" t="s">
         <v>18</v>
@@ -10156,10 +10163,10 @@
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A287" s="3" t="s">
-        <v>5</v>
+        <v>277</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>126</v>
+        <v>300</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>7</v>
@@ -10168,7 +10175,7 @@
         <v>8</v>
       </c>
       <c r="E287" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F287" t="s">
         <v>14</v>
@@ -10176,8 +10183,8 @@
       <c r="G287" t="s">
         <v>8</v>
       </c>
-      <c r="H287" s="8">
-        <v>5672</v>
+      <c r="H287" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I287" s="1" t="s">
         <v>18</v>
@@ -10188,7 +10195,7 @@
         <v>5</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>64</v>
+        <v>126</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>7</v>
@@ -10197,7 +10204,7 @@
         <v>8</v>
       </c>
       <c r="E288" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F288" t="s">
         <v>14</v>
@@ -10205,19 +10212,19 @@
       <c r="G288" t="s">
         <v>8</v>
       </c>
-      <c r="H288" s="8">
-        <v>5672</v>
+      <c r="H288" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I288" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A289" s="3" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>7</v>
@@ -10226,27 +10233,27 @@
         <v>8</v>
       </c>
       <c r="E289" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F289" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G289" t="s">
         <v>8</v>
       </c>
-      <c r="H289" s="8">
-        <v>5672</v>
+      <c r="H289" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I289" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A290" s="3" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>7</v>
@@ -10255,7 +10262,7 @@
         <v>8</v>
       </c>
       <c r="E290" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F290" t="s">
         <v>33</v>
@@ -10263,11 +10270,11 @@
       <c r="G290" t="s">
         <v>8</v>
       </c>
-      <c r="H290" s="8">
-        <v>5672</v>
+      <c r="H290" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I290" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.35">
@@ -10275,7 +10282,7 @@
         <v>5</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>7</v>
@@ -10284,27 +10291,27 @@
         <v>8</v>
       </c>
       <c r="E291" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F291" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G291" t="s">
         <v>8</v>
       </c>
-      <c r="H291" s="8">
-        <v>5672</v>
+      <c r="H291" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I291" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A292" s="3" t="s">
-        <v>228</v>
+        <v>5</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>7</v>
@@ -10321,22 +10328,22 @@
       <c r="G292" t="s">
         <v>8</v>
       </c>
-      <c r="H292" s="8">
-        <v>5672</v>
+      <c r="H292" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I292" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A293" s="3" t="s">
-        <v>395</v>
+        <v>228</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>396</v>
+        <v>51</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="D293" t="s">
         <v>8</v>
@@ -10350,8 +10357,8 @@
       <c r="G293" t="s">
         <v>8</v>
       </c>
-      <c r="H293" s="8">
-        <v>5672</v>
+      <c r="H293" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I293" s="1" t="s">
         <v>22</v>
@@ -10359,13 +10366,13 @@
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A294" s="3" t="s">
-        <v>80</v>
+        <v>395</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>39</v>
+        <v>396</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D294" t="s">
         <v>8</v>
@@ -10379,22 +10386,22 @@
       <c r="G294" t="s">
         <v>8</v>
       </c>
-      <c r="H294" s="8">
-        <v>5672</v>
+      <c r="H294" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I294" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A295" s="3" t="s">
-        <v>397</v>
+        <v>80</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>155</v>
+        <v>39</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D295" t="s">
         <v>8</v>
@@ -10408,8 +10415,8 @@
       <c r="G295" t="s">
         <v>8</v>
       </c>
-      <c r="H295" s="8">
-        <v>5672</v>
+      <c r="H295" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I295" s="1" t="s">
         <v>15</v>
@@ -10417,13 +10424,13 @@
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A296" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>398</v>
+        <v>155</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D296" t="s">
         <v>8</v>
@@ -10437,8 +10444,8 @@
       <c r="G296" t="s">
         <v>8</v>
       </c>
-      <c r="H296" s="8">
-        <v>5672</v>
+      <c r="H296" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I296" s="1" t="s">
         <v>15</v>
@@ -10446,13 +10453,13 @@
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A297" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>49</v>
+        <v>398</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="D297" t="s">
         <v>8</v>
@@ -10466,19 +10473,19 @@
       <c r="G297" t="s">
         <v>8</v>
       </c>
-      <c r="H297" s="8">
-        <v>5672</v>
+      <c r="H297" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I297" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A298" s="3" t="s">
-        <v>344</v>
+        <v>399</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>400</v>
+        <v>49</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>7</v>
@@ -10495,19 +10502,19 @@
       <c r="G298" t="s">
         <v>8</v>
       </c>
-      <c r="H298" s="8">
-        <v>5672</v>
+      <c r="H298" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I298" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A299" s="3" t="s">
-        <v>45</v>
+        <v>344</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>147</v>
+        <v>400</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>7</v>
@@ -10516,19 +10523,19 @@
         <v>8</v>
       </c>
       <c r="E299" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="F299" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G299" t="s">
         <v>8</v>
       </c>
-      <c r="H299" s="8">
-        <v>5672</v>
+      <c r="H299" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I299" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.35">
@@ -10536,7 +10543,7 @@
         <v>45</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>29</v>
+        <v>147</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>7</v>
@@ -10545,27 +10552,27 @@
         <v>8</v>
       </c>
       <c r="E300" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F300" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G300" t="s">
         <v>8</v>
       </c>
-      <c r="H300" s="8">
-        <v>5672</v>
+      <c r="H300" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I300" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A301" s="3" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>7</v>
@@ -10574,7 +10581,7 @@
         <v>8</v>
       </c>
       <c r="E301" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F301" t="s">
         <v>33</v>
@@ -10582,11 +10589,11 @@
       <c r="G301" t="s">
         <v>8</v>
       </c>
-      <c r="H301" s="8">
-        <v>5672</v>
+      <c r="H301" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I301" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.35">
@@ -10594,7 +10601,7 @@
         <v>5</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>155</v>
+        <v>51</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>7</v>
@@ -10603,19 +10610,19 @@
         <v>8</v>
       </c>
       <c r="E302" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F302" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G302" t="s">
         <v>8</v>
       </c>
-      <c r="H302" s="8">
-        <v>5672</v>
+      <c r="H302" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I302" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.35">
@@ -10623,7 +10630,7 @@
         <v>5</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>7</v>
@@ -10632,16 +10639,16 @@
         <v>8</v>
       </c>
       <c r="E303" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F303" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G303" t="s">
         <v>8</v>
       </c>
-      <c r="H303" s="8">
-        <v>5672</v>
+      <c r="H303" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I303" s="1" t="s">
         <v>11</v>
@@ -10652,7 +10659,7 @@
         <v>5</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>7</v>
@@ -10661,27 +10668,27 @@
         <v>8</v>
       </c>
       <c r="E304" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F304" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="G304" t="s">
         <v>8</v>
       </c>
-      <c r="H304" s="8">
-        <v>5672</v>
+      <c r="H304" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I304" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A305" s="3" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>7</v>
@@ -10690,27 +10697,27 @@
         <v>8</v>
       </c>
       <c r="E305" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F305" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="G305" t="s">
         <v>8</v>
       </c>
-      <c r="H305" s="8">
-        <v>5672</v>
+      <c r="H305" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I305" s="1" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A306" s="3" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>7</v>
@@ -10719,27 +10726,27 @@
         <v>8</v>
       </c>
       <c r="E306" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F306" t="s">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="G306" t="s">
         <v>8</v>
       </c>
-      <c r="H306" s="8">
-        <v>5672</v>
+      <c r="H306" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I306" s="1" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A307" s="3" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>7</v>
@@ -10748,27 +10755,27 @@
         <v>8</v>
       </c>
       <c r="E307" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F307" t="s">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="G307" t="s">
         <v>8</v>
       </c>
-      <c r="H307" s="8">
-        <v>5672</v>
+      <c r="H307" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I307" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A308" s="3" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>7</v>
@@ -10777,27 +10784,27 @@
         <v>8</v>
       </c>
       <c r="E308" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F308" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G308" t="s">
         <v>8</v>
       </c>
-      <c r="H308" s="8">
-        <v>5672</v>
+      <c r="H308" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I308" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A309" s="3" t="s">
-        <v>411</v>
+        <v>45</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>412</v>
+        <v>51</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>7</v>
@@ -10806,27 +10813,27 @@
         <v>8</v>
       </c>
       <c r="E309" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="F309" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G309" t="s">
         <v>8</v>
       </c>
-      <c r="H309" s="8">
-        <v>5672</v>
+      <c r="H309" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I309" s="1" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A310" s="3" t="s">
-        <v>5</v>
+        <v>411</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>87</v>
+        <v>412</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>7</v>
@@ -10835,16 +10842,16 @@
         <v>8</v>
       </c>
       <c r="E310" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F310" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G310" t="s">
         <v>8</v>
       </c>
-      <c r="H310" s="8">
-        <v>5672</v>
+      <c r="H310" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I310" s="1" t="s">
         <v>60</v>
@@ -10855,7 +10862,7 @@
         <v>5</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>7</v>
@@ -10864,16 +10871,16 @@
         <v>8</v>
       </c>
       <c r="E311" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F311" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G311" t="s">
         <v>8</v>
       </c>
-      <c r="H311" s="8">
-        <v>5672</v>
+      <c r="H311" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I311" s="1" t="s">
         <v>60</v>
@@ -10884,7 +10891,7 @@
         <v>5</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>204</v>
+        <v>29</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>7</v>
@@ -10893,27 +10900,27 @@
         <v>8</v>
       </c>
       <c r="E312" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F312" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G312" t="s">
         <v>8</v>
       </c>
-      <c r="H312" s="8">
-        <v>5672</v>
+      <c r="H312" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I312" s="1" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A313" s="3" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>77</v>
+        <v>204</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>7</v>
@@ -10922,7 +10929,7 @@
         <v>8</v>
       </c>
       <c r="E313" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F313" t="s">
         <v>14</v>
@@ -10930,8 +10937,8 @@
       <c r="G313" t="s">
         <v>8</v>
       </c>
-      <c r="H313" s="8">
-        <v>5672</v>
+      <c r="H313" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I313" s="1" t="s">
         <v>22</v>
@@ -10939,10 +10946,10 @@
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A314" s="3" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>7</v>
@@ -10951,19 +10958,19 @@
         <v>8</v>
       </c>
       <c r="E314" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F314" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G314" t="s">
         <v>8</v>
       </c>
-      <c r="H314" s="8">
-        <v>5672</v>
+      <c r="H314" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I314" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.35">
@@ -10971,7 +10978,7 @@
         <v>5</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>6</v>
+        <v>126</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>7</v>
@@ -10980,7 +10987,7 @@
         <v>8</v>
       </c>
       <c r="E315" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F315" t="s">
         <v>33</v>
@@ -10988,11 +10995,11 @@
       <c r="G315" t="s">
         <v>8</v>
       </c>
-      <c r="H315" s="8">
-        <v>5672</v>
+      <c r="H315" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I315" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.35">
@@ -11000,7 +11007,7 @@
         <v>5</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>7</v>
@@ -11009,33 +11016,33 @@
         <v>8</v>
       </c>
       <c r="E316" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F316" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G316" t="s">
         <v>8</v>
       </c>
-      <c r="H316" s="8">
-        <v>5672</v>
+      <c r="H316" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I316" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A317" s="3" t="s">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D317" t="s">
-        <v>341</v>
+        <v>8</v>
       </c>
       <c r="E317" t="s">
         <v>419</v>
@@ -11046,8 +11053,8 @@
       <c r="G317" t="s">
         <v>8</v>
       </c>
-      <c r="H317" s="8">
-        <v>5672</v>
+      <c r="H317" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I317" s="1" t="s">
         <v>18</v>
@@ -11055,39 +11062,39 @@
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A318" s="3" t="s">
-        <v>420</v>
+        <v>61</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>420</v>
+        <v>23</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="D318" t="s">
-        <v>8</v>
+        <v>341</v>
       </c>
       <c r="E318" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F318" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G318" t="s">
         <v>8</v>
       </c>
-      <c r="H318" s="8">
-        <v>5672</v>
+      <c r="H318" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I318" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A319" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>47</v>
@@ -11104,8 +11111,8 @@
       <c r="G319" t="s">
         <v>8</v>
       </c>
-      <c r="H319" s="8">
-        <v>5672</v>
+      <c r="H319" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I319" s="1" t="s">
         <v>22</v>
@@ -11113,71 +11120,71 @@
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A320" s="3" t="s">
-        <v>45</v>
+        <v>422</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>84</v>
+        <v>422</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="D320" t="s">
         <v>8</v>
       </c>
       <c r="E320" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F320" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G320" t="s">
         <v>8</v>
       </c>
-      <c r="H320" s="8">
-        <v>5672</v>
+      <c r="H320" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I320" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A321" s="3" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="D321" t="s">
         <v>8</v>
       </c>
       <c r="E321" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F321" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G321" t="s">
         <v>8</v>
       </c>
-      <c r="H321" s="8">
-        <v>5672</v>
+      <c r="H321" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I321" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A322" s="3" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>29</v>
+        <v>126</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D322" t="s">
         <v>8</v>
@@ -11191,19 +11198,19 @@
       <c r="G322" t="s">
         <v>8</v>
       </c>
-      <c r="H322" s="8">
-        <v>5672</v>
+      <c r="H322" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I322" s="1" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A323" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>43</v>
@@ -11220,22 +11227,22 @@
       <c r="G323" t="s">
         <v>8</v>
       </c>
-      <c r="H323" s="8">
-        <v>5672</v>
+      <c r="H323" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I323" s="1" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A324" s="3" t="s">
-        <v>395</v>
+        <v>48</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>164</v>
+        <v>51</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="D324" t="s">
         <v>8</v>
@@ -11249,8 +11256,8 @@
       <c r="G324" t="s">
         <v>8</v>
       </c>
-      <c r="H324" s="8">
-        <v>5672</v>
+      <c r="H324" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I324" s="1" t="s">
         <v>22</v>
@@ -11258,10 +11265,10 @@
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A325" s="3" t="s">
-        <v>28</v>
+        <v>395</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>7</v>
@@ -11270,27 +11277,27 @@
         <v>8</v>
       </c>
       <c r="E325" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="F325" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G325" t="s">
         <v>8</v>
       </c>
-      <c r="H325" s="8">
-        <v>5672</v>
+      <c r="H325" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I325" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A326" s="3" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>7</v>
@@ -11299,27 +11306,27 @@
         <v>8</v>
       </c>
       <c r="E326" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F326" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G326" t="s">
         <v>8</v>
       </c>
-      <c r="H326" s="8">
-        <v>5672</v>
+      <c r="H326" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I326" s="1" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A327" s="3" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>6</v>
+        <v>147</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>7</v>
@@ -11328,7 +11335,7 @@
         <v>8</v>
       </c>
       <c r="E327" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F327" t="s">
         <v>33</v>
@@ -11336,19 +11343,19 @@
       <c r="G327" t="s">
         <v>8</v>
       </c>
-      <c r="H327" s="8">
-        <v>5672</v>
+      <c r="H327" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I327" s="1" t="s">
-        <v>11</v>
+        <v>60</v>
       </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A328" s="3" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>87</v>
+        <v>6</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>7</v>
@@ -11357,16 +11364,16 @@
         <v>8</v>
       </c>
       <c r="E328" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F328" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G328" t="s">
         <v>8</v>
       </c>
-      <c r="H328" s="8">
-        <v>5672</v>
+      <c r="H328" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I328" s="1" t="s">
         <v>11</v>
@@ -11374,10 +11381,10 @@
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A329" s="3" t="s">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>7</v>
@@ -11386,7 +11393,7 @@
         <v>8</v>
       </c>
       <c r="E329" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F329" t="s">
         <v>21</v>
@@ -11394,19 +11401,19 @@
       <c r="G329" t="s">
         <v>8</v>
       </c>
-      <c r="H329" s="8">
-        <v>5672</v>
+      <c r="H329" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I329" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A330" s="3" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>7</v>
@@ -11415,19 +11422,19 @@
         <v>8</v>
       </c>
       <c r="E330" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F330" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G330" t="s">
         <v>8</v>
       </c>
-      <c r="H330" s="8">
-        <v>5672</v>
+      <c r="H330" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I330" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.35">
@@ -11435,7 +11442,7 @@
         <v>5</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>7</v>
@@ -11444,19 +11451,19 @@
         <v>8</v>
       </c>
       <c r="E331" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F331" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G331" t="s">
         <v>8</v>
       </c>
-      <c r="H331" s="8">
-        <v>5672</v>
+      <c r="H331" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I331" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.35">
@@ -11464,16 +11471,16 @@
         <v>5</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>87</v>
+        <v>6</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="D332" t="s">
         <v>8</v>
       </c>
       <c r="E332" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F332" t="s">
         <v>14</v>
@@ -11481,22 +11488,22 @@
       <c r="G332" t="s">
         <v>8</v>
       </c>
-      <c r="H332" s="8">
-        <v>5672</v>
+      <c r="H332" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I332" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A333" s="3" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D333" t="s">
         <v>8</v>
@@ -11510,22 +11517,22 @@
       <c r="G333" t="s">
         <v>8</v>
       </c>
-      <c r="H333" s="8">
-        <v>5672</v>
+      <c r="H333" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I333" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A334" s="3" t="s">
-        <v>332</v>
+        <v>45</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>432</v>
+        <v>91</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="D334" t="s">
         <v>8</v>
@@ -11539,19 +11546,19 @@
       <c r="G334" t="s">
         <v>8</v>
       </c>
-      <c r="H334" s="8">
-        <v>5672</v>
+      <c r="H334" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I334" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A335" s="3" t="s">
-        <v>5</v>
+        <v>332</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>6</v>
+        <v>432</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>7</v>
@@ -11560,27 +11567,27 @@
         <v>8</v>
       </c>
       <c r="E335" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F335" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G335" t="s">
         <v>8</v>
       </c>
-      <c r="H335" s="8">
-        <v>5672</v>
+      <c r="H335" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I335" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A336" s="3" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>155</v>
+        <v>6</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>7</v>
@@ -11589,27 +11596,27 @@
         <v>8</v>
       </c>
       <c r="E336" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F336" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G336" t="s">
         <v>8</v>
       </c>
-      <c r="H336" s="8">
-        <v>5672</v>
+      <c r="H336" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I336" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A337" s="3" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>23</v>
+        <v>155</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>7</v>
@@ -11618,7 +11625,7 @@
         <v>8</v>
       </c>
       <c r="E337" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F337" t="s">
         <v>14</v>
@@ -11626,8 +11633,8 @@
       <c r="G337" t="s">
         <v>8</v>
       </c>
-      <c r="H337" s="8">
-        <v>5672</v>
+      <c r="H337" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I337" s="1" t="s">
         <v>18</v>
@@ -11638,7 +11645,7 @@
         <v>5</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>436</v>
+        <v>23</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>7</v>
@@ -11647,7 +11654,7 @@
         <v>8</v>
       </c>
       <c r="E338" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F338" t="s">
         <v>14</v>
@@ -11655,11 +11662,11 @@
       <c r="G338" t="s">
         <v>8</v>
       </c>
-      <c r="H338" s="8">
-        <v>5672</v>
+      <c r="H338" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I338" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.35">
@@ -11667,7 +11674,7 @@
         <v>5</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>51</v>
+        <v>436</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>7</v>
@@ -11676,7 +11683,7 @@
         <v>8</v>
       </c>
       <c r="E339" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F339" t="s">
         <v>14</v>
@@ -11684,8 +11691,8 @@
       <c r="G339" t="s">
         <v>8</v>
       </c>
-      <c r="H339" s="8">
-        <v>5672</v>
+      <c r="H339" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I339" s="1" t="s">
         <v>15</v>
@@ -11693,10 +11700,10 @@
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A340" s="3" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>7</v>
@@ -11705,27 +11712,27 @@
         <v>8</v>
       </c>
       <c r="E340" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F340" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G340" t="s">
         <v>8</v>
       </c>
-      <c r="H340" s="8">
-        <v>5672</v>
+      <c r="H340" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I340" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A341" s="3" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>7</v>
@@ -11734,27 +11741,27 @@
         <v>8</v>
       </c>
       <c r="E341" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F341" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G341" t="s">
         <v>8</v>
       </c>
-      <c r="H341" s="8">
-        <v>5672</v>
+      <c r="H341" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I341" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A342" s="3" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>7</v>
@@ -11763,16 +11770,16 @@
         <v>8</v>
       </c>
       <c r="E342" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F342" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G342" t="s">
         <v>8</v>
       </c>
-      <c r="H342" s="8">
-        <v>5672</v>
+      <c r="H342" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I342" s="1" t="s">
         <v>15</v>
@@ -11780,10 +11787,10 @@
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A343" s="3" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>7</v>
@@ -11792,19 +11799,19 @@
         <v>8</v>
       </c>
       <c r="E343" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F343" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G343" t="s">
         <v>8</v>
       </c>
-      <c r="H343" s="8">
-        <v>5672</v>
+      <c r="H343" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I343" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.35">
@@ -11821,7 +11828,7 @@
         <v>8</v>
       </c>
       <c r="E344" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F344" t="s">
         <v>14</v>
@@ -11829,11 +11836,11 @@
       <c r="G344" t="s">
         <v>8</v>
       </c>
-      <c r="H344" s="8">
-        <v>5672</v>
+      <c r="H344" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I344" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.35">
@@ -11841,7 +11848,7 @@
         <v>5</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>7</v>
@@ -11850,7 +11857,7 @@
         <v>8</v>
       </c>
       <c r="E345" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F345" t="s">
         <v>14</v>
@@ -11858,11 +11865,11 @@
       <c r="G345" t="s">
         <v>8</v>
       </c>
-      <c r="H345" s="8">
-        <v>5672</v>
+      <c r="H345" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I345" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.35">
@@ -11876,22 +11883,22 @@
         <v>7</v>
       </c>
       <c r="D346" t="s">
-        <v>341</v>
+        <v>8</v>
       </c>
       <c r="E346" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F346" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G346" t="s">
         <v>8</v>
       </c>
-      <c r="H346" s="8">
-        <v>5672</v>
+      <c r="H346" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I346" s="1" t="s">
-        <v>128</v>
+        <v>22</v>
       </c>
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.35">
@@ -11899,36 +11906,36 @@
         <v>5</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D347" t="s">
-        <v>8</v>
+        <v>341</v>
       </c>
       <c r="E347" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F347" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G347" t="s">
         <v>8</v>
       </c>
-      <c r="H347" s="8">
-        <v>5672</v>
+      <c r="H347" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I347" s="1" t="s">
-        <v>18</v>
+        <v>128</v>
       </c>
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A348" s="3" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>7</v>
@@ -11937,16 +11944,16 @@
         <v>8</v>
       </c>
       <c r="E348" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F348" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G348" t="s">
         <v>8</v>
       </c>
-      <c r="H348" s="8">
-        <v>5672</v>
+      <c r="H348" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I348" s="1" t="s">
         <v>18</v>
@@ -11954,10 +11961,10 @@
     </row>
     <row r="349" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A349" s="3" t="s">
-        <v>346</v>
+        <v>28</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>436</v>
+        <v>49</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>7</v>
@@ -11974,19 +11981,19 @@
       <c r="G349" t="s">
         <v>8</v>
       </c>
-      <c r="H349" s="8">
-        <v>5672</v>
+      <c r="H349" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I349" s="1" t="s">
-        <v>128</v>
+        <v>18</v>
       </c>
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A350" s="3" t="s">
-        <v>5</v>
+        <v>346</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>29</v>
+        <v>436</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>7</v>
@@ -11995,19 +12002,19 @@
         <v>8</v>
       </c>
       <c r="E350" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F350" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G350" t="s">
         <v>8</v>
       </c>
-      <c r="H350" s="8">
-        <v>5672</v>
+      <c r="H350" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I350" s="1" t="s">
-        <v>15</v>
+        <v>128</v>
       </c>
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.35">
@@ -12015,7 +12022,7 @@
         <v>5</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>7</v>
@@ -12024,16 +12031,16 @@
         <v>8</v>
       </c>
       <c r="E351" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F351" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G351" t="s">
         <v>8</v>
       </c>
-      <c r="H351" s="8">
-        <v>5672</v>
+      <c r="H351" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I351" s="1" t="s">
         <v>15</v>
@@ -12041,19 +12048,19 @@
     </row>
     <row r="352" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A352" s="3" t="s">
-        <v>450</v>
+        <v>5</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>451</v>
+        <v>64</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="D352" t="s">
         <v>8</v>
       </c>
       <c r="E352" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="F352" t="s">
         <v>14</v>
@@ -12061,22 +12068,22 @@
       <c r="G352" t="s">
         <v>8</v>
       </c>
-      <c r="H352" s="8">
-        <v>5672</v>
+      <c r="H352" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I352" s="1" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A353" s="3" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D353" t="s">
         <v>8</v>
@@ -12090,8 +12097,8 @@
       <c r="G353" t="s">
         <v>8</v>
       </c>
-      <c r="H353" s="8">
-        <v>5672</v>
+      <c r="H353" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I353" s="1" t="s">
         <v>60</v>
@@ -12099,10 +12106,10 @@
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A354" s="3" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>43</v>
@@ -12119,19 +12126,19 @@
       <c r="G354" t="s">
         <v>8</v>
       </c>
-      <c r="H354" s="8">
-        <v>5672</v>
+      <c r="H354" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I354" s="1" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A355" s="3" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>43</v>
@@ -12148,22 +12155,22 @@
       <c r="G355" t="s">
         <v>8</v>
       </c>
-      <c r="H355" s="8">
-        <v>5672</v>
+      <c r="H355" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I355" s="1" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A356" s="3" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>276</v>
+        <v>458</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="D356" t="s">
         <v>8</v>
@@ -12177,19 +12184,19 @@
       <c r="G356" t="s">
         <v>8</v>
       </c>
-      <c r="H356" s="8">
-        <v>5672</v>
+      <c r="H356" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I356" s="1" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A357" s="3" t="s">
-        <v>5</v>
+        <v>459</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>29</v>
+        <v>276</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>7</v>
@@ -12198,16 +12205,16 @@
         <v>8</v>
       </c>
       <c r="E357" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="F357" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G357" t="s">
         <v>8</v>
       </c>
-      <c r="H357" s="8">
-        <v>5672</v>
+      <c r="H357" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I357" s="1" t="s">
         <v>15</v>
@@ -12218,7 +12225,7 @@
         <v>5</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>7</v>
@@ -12227,19 +12234,19 @@
         <v>8</v>
       </c>
       <c r="E358" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F358" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G358" t="s">
         <v>8</v>
       </c>
-      <c r="H358" s="8">
-        <v>5672</v>
+      <c r="H358" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I358" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="359" spans="1:9" x14ac:dyDescent="0.35">
@@ -12247,7 +12254,7 @@
         <v>5</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>130</v>
+        <v>37</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>7</v>
@@ -12259,13 +12266,13 @@
         <v>461</v>
       </c>
       <c r="F359" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G359" t="s">
         <v>8</v>
       </c>
-      <c r="H359" s="8">
-        <v>5672</v>
+      <c r="H359" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I359" s="1" t="s">
         <v>18</v>
@@ -12276,7 +12283,7 @@
         <v>5</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>37</v>
+        <v>130</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>7</v>
@@ -12285,7 +12292,7 @@
         <v>8</v>
       </c>
       <c r="E360" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F360" t="s">
         <v>14</v>
@@ -12293,8 +12300,8 @@
       <c r="G360" t="s">
         <v>8</v>
       </c>
-      <c r="H360" s="8">
-        <v>5672</v>
+      <c r="H360" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I360" s="1" t="s">
         <v>18</v>
@@ -12305,7 +12312,7 @@
         <v>5</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>7</v>
@@ -12314,7 +12321,7 @@
         <v>8</v>
       </c>
       <c r="E361" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F361" t="s">
         <v>14</v>
@@ -12322,11 +12329,11 @@
       <c r="G361" t="s">
         <v>8</v>
       </c>
-      <c r="H361" s="8">
-        <v>5672</v>
+      <c r="H361" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I361" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.35">
@@ -12334,7 +12341,7 @@
         <v>5</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>7</v>
@@ -12343,19 +12350,19 @@
         <v>8</v>
       </c>
       <c r="E362" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F362" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="G362" t="s">
         <v>8</v>
       </c>
-      <c r="H362" s="8">
-        <v>5672</v>
+      <c r="H362" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I362" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.35">
@@ -12372,19 +12379,19 @@
         <v>8</v>
       </c>
       <c r="E363" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F363" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="G363" t="s">
         <v>8</v>
       </c>
-      <c r="H363" s="8">
-        <v>5672</v>
+      <c r="H363" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I363" s="1" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
     </row>
     <row r="364" spans="1:9" x14ac:dyDescent="0.35">
@@ -12392,7 +12399,7 @@
         <v>5</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>7</v>
@@ -12401,16 +12408,16 @@
         <v>8</v>
       </c>
       <c r="E364" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F364" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G364" t="s">
         <v>8</v>
       </c>
-      <c r="H364" s="8">
-        <v>5672</v>
+      <c r="H364" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I364" s="1" t="s">
         <v>60</v>
@@ -12421,7 +12428,7 @@
         <v>5</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>7</v>
@@ -12430,19 +12437,19 @@
         <v>8</v>
       </c>
       <c r="E365" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F365" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G365" t="s">
         <v>8</v>
       </c>
-      <c r="H365" s="8">
-        <v>5672</v>
+      <c r="H365" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I365" s="1" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.35">
@@ -12450,7 +12457,7 @@
         <v>5</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>7</v>
@@ -12459,7 +12466,7 @@
         <v>8</v>
       </c>
       <c r="E366" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F366" t="s">
         <v>33</v>
@@ -12467,19 +12474,19 @@
       <c r="G366" t="s">
         <v>8</v>
       </c>
-      <c r="H366" s="8">
-        <v>5672</v>
+      <c r="H366" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I366" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A367" s="3" t="s">
-        <v>469</v>
+        <v>5</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>7</v>
@@ -12488,7 +12495,7 @@
         <v>8</v>
       </c>
       <c r="E367" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="F367" t="s">
         <v>33</v>
@@ -12496,19 +12503,19 @@
       <c r="G367" t="s">
         <v>8</v>
       </c>
-      <c r="H367" s="8">
-        <v>5672</v>
+      <c r="H367" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I367" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="368" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A368" s="3" t="s">
-        <v>5</v>
+        <v>469</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>7</v>
@@ -12517,19 +12524,19 @@
         <v>8</v>
       </c>
       <c r="E368" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F368" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G368" t="s">
         <v>8</v>
       </c>
-      <c r="H368" s="8">
-        <v>5672</v>
+      <c r="H368" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I368" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.35">
@@ -12546,16 +12553,16 @@
         <v>8</v>
       </c>
       <c r="E369" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F369" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G369" t="s">
         <v>8</v>
       </c>
-      <c r="H369" s="8">
-        <v>5672</v>
+      <c r="H369" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I369" s="1" t="s">
         <v>22</v>
@@ -12566,7 +12573,7 @@
         <v>5</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>473</v>
+        <v>29</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>7</v>
@@ -12575,7 +12582,7 @@
         <v>8</v>
       </c>
       <c r="E370" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F370" t="s">
         <v>33</v>
@@ -12583,8 +12590,8 @@
       <c r="G370" t="s">
         <v>8</v>
       </c>
-      <c r="H370" s="8">
-        <v>5672</v>
+      <c r="H370" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I370" s="1" t="s">
         <v>22</v>
@@ -12595,7 +12602,7 @@
         <v>5</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>12</v>
+        <v>473</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>7</v>
@@ -12604,19 +12611,19 @@
         <v>8</v>
       </c>
       <c r="E371" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F371" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G371" t="s">
         <v>8</v>
       </c>
-      <c r="H371" s="8">
-        <v>5672</v>
+      <c r="H371" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I371" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="372" spans="1:9" x14ac:dyDescent="0.35">
@@ -12624,7 +12631,7 @@
         <v>5</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>7</v>
@@ -12633,7 +12640,7 @@
         <v>8</v>
       </c>
       <c r="E372" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F372" t="s">
         <v>14</v>
@@ -12641,8 +12648,8 @@
       <c r="G372" t="s">
         <v>8</v>
       </c>
-      <c r="H372" s="8">
-        <v>5672</v>
+      <c r="H372" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I372" s="1" t="s">
         <v>11</v>
@@ -12653,7 +12660,7 @@
         <v>5</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>7</v>
@@ -12662,7 +12669,7 @@
         <v>8</v>
       </c>
       <c r="E373" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F373" t="s">
         <v>14</v>
@@ -12670,11 +12677,11 @@
       <c r="G373" t="s">
         <v>8</v>
       </c>
-      <c r="H373" s="8">
-        <v>5672</v>
+      <c r="H373" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I373" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.35">
@@ -12682,7 +12689,7 @@
         <v>5</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>7</v>
@@ -12691,7 +12698,7 @@
         <v>8</v>
       </c>
       <c r="E374" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F374" t="s">
         <v>14</v>
@@ -12699,19 +12706,19 @@
       <c r="G374" t="s">
         <v>8</v>
       </c>
-      <c r="H374" s="8">
-        <v>5672</v>
+      <c r="H374" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I374" s="1" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A375" s="3" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>7</v>
@@ -12720,7 +12727,7 @@
         <v>8</v>
       </c>
       <c r="E375" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F375" t="s">
         <v>14</v>
@@ -12728,8 +12735,8 @@
       <c r="G375" t="s">
         <v>8</v>
       </c>
-      <c r="H375" s="8">
-        <v>5672</v>
+      <c r="H375" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="I375" s="1" t="s">
         <v>60</v>
@@ -12737,52 +12744,81 @@
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A376" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B376" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C376" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D376" t="s">
+        <v>8</v>
+      </c>
+      <c r="E376" t="s">
+        <v>479</v>
+      </c>
+      <c r="F376" t="s">
+        <v>14</v>
+      </c>
+      <c r="G376" t="s">
+        <v>8</v>
+      </c>
+      <c r="H376" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="I376" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="377" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A377" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="B376" s="3" t="s">
+      <c r="B377" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="C376" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D376" t="s">
-        <v>8</v>
-      </c>
-      <c r="E376" t="s">
+      <c r="C377" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D377" t="s">
+        <v>8</v>
+      </c>
+      <c r="E377" t="s">
         <v>482</v>
       </c>
-      <c r="F376" t="s">
-        <v>14</v>
-      </c>
-      <c r="G376" t="s">
-        <v>8</v>
-      </c>
-      <c r="H376" s="8">
-        <v>5672</v>
-      </c>
-      <c r="I376" s="1" t="s">
+      <c r="F377" t="s">
+        <v>14</v>
+      </c>
+      <c r="G377" t="s">
+        <v>8</v>
+      </c>
+      <c r="H377" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="I377" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A377" s="6" t="s">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A378" s="6" t="s">
         <v>483</v>
       </c>
-      <c r="B377" s="6"/>
-      <c r="C377" s="6"/>
-      <c r="D377" t="s">
-        <v>8</v>
-      </c>
-      <c r="E377" t="s">
-        <v>8</v>
-      </c>
-      <c r="F377" t="s">
-        <v>8</v>
-      </c>
-      <c r="G377" t="s">
-        <v>8</v>
-      </c>
-      <c r="H377" s="8" t="s">
+      <c r="B378" s="6"/>
+      <c r="C378" s="6"/>
+      <c r="D378" t="s">
+        <v>8</v>
+      </c>
+      <c r="E378" t="s">
+        <v>8</v>
+      </c>
+      <c r="F378" t="s">
+        <v>8</v>
+      </c>
+      <c r="G378" t="s">
+        <v>8</v>
+      </c>
+      <c r="H378" s="8" t="s">
         <v>8</v>
       </c>
     </row>
@@ -12791,9 +12827,10 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="D2:G2"/>
-    <mergeCell ref="A377:C377"/>
+    <mergeCell ref="A378:C378"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>